--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O572"/>
+  <dimension ref="A1:O579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25537,7 +25537,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr"/>
       <c r="M527" t="inlineStr">
         <is>
@@ -26151,7 +26155,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="L536" t="inlineStr"/>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="M536" t="inlineStr">
         <is>
           <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -26281,7 +26289,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="L538" t="inlineStr"/>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="M538" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación (Segundo Procedimiento)</t>
@@ -26407,7 +26419,11 @@
         </is>
       </c>
       <c r="K540" t="inlineStr"/>
-      <c r="L540" t="inlineStr"/>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="M540" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -26472,7 +26488,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr"/>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="M541" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -26537,7 +26557,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="L542" t="inlineStr"/>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="M542" t="inlineStr">
         <is>
           <t>Combustibles y Lubricantes para Vehículos y Equipos Terrestres</t>
@@ -26597,7 +26621,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr"/>
       <c r="M543" t="inlineStr">
         <is>
@@ -26658,7 +26686,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr"/>
       <c r="M544" t="inlineStr">
         <is>
@@ -26719,7 +26751,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr"/>
       <c r="M545" t="inlineStr">
         <is>
@@ -26777,7 +26813,7 @@
       <c r="I546" t="inlineStr"/>
       <c r="J546" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="K546" t="inlineStr"/>
@@ -26841,7 +26877,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr">
         <is>
@@ -27507,7 +27547,11 @@
       </c>
       <c r="H558" t="inlineStr"/>
       <c r="I558" t="inlineStr"/>
-      <c r="J558" t="inlineStr"/>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K558" t="inlineStr"/>
       <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
@@ -27564,7 +27608,11 @@
       </c>
       <c r="H559" t="inlineStr"/>
       <c r="I559" t="inlineStr"/>
-      <c r="J559" t="inlineStr"/>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K559" t="inlineStr"/>
       <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr">
@@ -27682,7 +27730,11 @@
       </c>
       <c r="H561" t="inlineStr"/>
       <c r="I561" t="inlineStr"/>
-      <c r="J561" t="inlineStr"/>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K561" t="inlineStr"/>
       <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
@@ -27739,7 +27791,11 @@
       </c>
       <c r="H562" t="inlineStr"/>
       <c r="I562" t="inlineStr"/>
-      <c r="J562" t="inlineStr"/>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K562" t="inlineStr"/>
       <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
@@ -28081,7 +28137,11 @@
       </c>
       <c r="H568" t="inlineStr"/>
       <c r="I568" t="inlineStr"/>
-      <c r="J568" t="inlineStr"/>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
       <c r="K568" t="inlineStr"/>
       <c r="L568" t="inlineStr"/>
       <c r="M568" t="inlineStr">
@@ -28328,6 +28388,405 @@
         </is>
       </c>
     </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0572-2026</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+      <c r="J573" t="inlineStr"/>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Mobiliario y Equipamiento de Oficina (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N573" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0572-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0573-2026</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+      <c r="J574" t="inlineStr"/>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0573-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0574-2026</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+      <c r="J575" t="inlineStr"/>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios Y Suministros Médicos</t>
+        </is>
+      </c>
+      <c r="N575" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Pachuca</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0574-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0575-2026</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
+      <c r="J576" t="inlineStr"/>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería, Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N576" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0575-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0576-2026</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr"/>
+      <c r="J577" t="inlineStr"/>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Servicios de Informática</t>
+        </is>
+      </c>
+      <c r="N577" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0576-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0577-2026</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
+      <c r="J578" t="inlineStr"/>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N578" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0577-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0578-2026</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+      <c r="J579" t="inlineStr"/>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N579" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0578-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O579"/>
+  <dimension ref="A1:O587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23374,7 +23374,11 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="L495" t="inlineStr"/>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
       <c r="M495" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Equipo de café)</t>
@@ -25408,7 +25412,11 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="L525" t="inlineStr"/>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M525" t="inlineStr">
         <is>
           <t>Ayudas Sociales A Personas</t>
@@ -25542,7 +25550,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr"/>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M527" t="inlineStr">
         <is>
           <t>Prendas de Protección para Seguridad Pública</t>
@@ -26626,7 +26638,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="L543" t="inlineStr"/>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M543" t="inlineStr">
         <is>
           <t>Servicios Integrales de Telecomunicaciones y Redes de Transporte de Información</t>
@@ -26691,7 +26707,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="L544" t="inlineStr"/>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M544" t="inlineStr">
         <is>
           <t>Servicios de Internet</t>
@@ -26756,7 +26776,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="L545" t="inlineStr"/>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M545" t="inlineStr">
         <is>
           <t>Servicios Legales</t>
@@ -26942,7 +26966,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr"/>
       <c r="M548" t="inlineStr">
         <is>
@@ -27003,7 +27031,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr"/>
       <c r="M549" t="inlineStr">
         <is>
@@ -27064,7 +27096,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr"/>
       <c r="M550" t="inlineStr">
         <is>
@@ -27125,7 +27161,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr">
         <is>
@@ -27186,7 +27226,11 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr">
         <is>
@@ -27674,8 +27718,16 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
-      <c r="L560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M560" t="inlineStr">
         <is>
           <t>Conservación y Mantenimiento Menor de Inmuebles</t>
@@ -27852,7 +27904,11 @@
       </c>
       <c r="H563" t="inlineStr"/>
       <c r="I563" t="inlineStr"/>
-      <c r="J563" t="inlineStr"/>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K563" t="inlineStr"/>
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
@@ -27909,7 +27965,11 @@
       </c>
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr"/>
-      <c r="J564" t="inlineStr"/>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K564" t="inlineStr"/>
       <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
@@ -27966,7 +28026,11 @@
       </c>
       <c r="H565" t="inlineStr"/>
       <c r="I565" t="inlineStr"/>
-      <c r="J565" t="inlineStr"/>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K565" t="inlineStr"/>
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
@@ -28023,7 +28087,11 @@
       </c>
       <c r="H566" t="inlineStr"/>
       <c r="I566" t="inlineStr"/>
-      <c r="J566" t="inlineStr"/>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K566" t="inlineStr"/>
       <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
@@ -28080,7 +28148,11 @@
       </c>
       <c r="H567" t="inlineStr"/>
       <c r="I567" t="inlineStr"/>
-      <c r="J567" t="inlineStr"/>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="K567" t="inlineStr"/>
       <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
@@ -28787,6 +28859,462 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0579-2026</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
+      <c r="J580" t="inlineStr"/>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (colchones)</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0579-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0580-2026</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+      <c r="J581" t="inlineStr"/>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Módulos de Invernadero) (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr">
+        <is>
+          <t>la Dirección General de Desarrollo Rural de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0580-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0581-2026</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+      <c r="J582" t="inlineStr"/>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0581-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0582-2026</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr"/>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N583" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0582-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0583-2026</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+      <c r="J584" t="inlineStr"/>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N584" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0583-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0584-2026</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+      <c r="J585" t="inlineStr"/>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos, Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0584-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0585-2026</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+      <c r="J586" t="inlineStr"/>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>Combustibles y Lubricantes Para Vehículos y Equipos Terrestres</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>el Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0585-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0586-2026</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
+      <c r="J587" t="inlineStr"/>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>Combustibles y Lubricantes Para Vehículos y Equipos Terrestres</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>el Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0586-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O587"/>
+  <dimension ref="A1:O594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26971,7 +26971,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L548" t="inlineStr"/>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M548" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -27036,7 +27040,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L549" t="inlineStr"/>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M549" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -27101,7 +27109,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L550" t="inlineStr"/>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M550" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -27166,7 +27178,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L551" t="inlineStr"/>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M551" t="inlineStr">
         <is>
           <t>Donativos a Entes Públicos Estatales y Municipales</t>
@@ -27231,7 +27247,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="L552" t="inlineStr"/>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M552" t="inlineStr">
         <is>
           <t>Seguro de Accidentes Escolares</t>
@@ -27291,7 +27311,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr">
         <is>
@@ -27352,7 +27376,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr"/>
       <c r="M554" t="inlineStr">
         <is>
@@ -27413,7 +27441,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr"/>
       <c r="M555" t="inlineStr">
         <is>
@@ -27474,7 +27506,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr"/>
       <c r="M556" t="inlineStr">
         <is>
@@ -27535,7 +27571,11 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr"/>
       <c r="M557" t="inlineStr">
         <is>
@@ -28214,8 +28254,16 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
-      <c r="L568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="M568" t="inlineStr">
         <is>
           <t>Otros Arrendamientos (Segundo Procedimiento)</t>
@@ -28270,7 +28318,11 @@
       </c>
       <c r="H569" t="inlineStr"/>
       <c r="I569" t="inlineStr"/>
-      <c r="J569" t="inlineStr"/>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="K569" t="inlineStr"/>
       <c r="L569" t="inlineStr"/>
       <c r="M569" t="inlineStr">
@@ -28384,7 +28436,11 @@
       </c>
       <c r="H571" t="inlineStr"/>
       <c r="I571" t="inlineStr"/>
-      <c r="J571" t="inlineStr"/>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="K571" t="inlineStr"/>
       <c r="L571" t="inlineStr"/>
       <c r="M571" t="inlineStr">
@@ -28441,7 +28497,11 @@
       </c>
       <c r="H572" t="inlineStr"/>
       <c r="I572" t="inlineStr"/>
-      <c r="J572" t="inlineStr"/>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
       <c r="K572" t="inlineStr"/>
       <c r="L572" t="inlineStr"/>
       <c r="M572" t="inlineStr">
@@ -29315,6 +29375,405 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0587-2026</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+      <c r="J588" t="inlineStr"/>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0587-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0588-2026</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+      <c r="J589" t="inlineStr"/>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros Médicos (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0588-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0589-2026</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr"/>
+      <c r="J590" t="inlineStr"/>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>Equipo educativo para el Laboratorio de Innovación Agrícola Sustentable (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>la Subdirección de Servicios Administrativos del Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0589-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0590-2026</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr"/>
+      <c r="J591" t="inlineStr"/>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Alimentación de Animales (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0590-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0591-2026</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr"/>
+      <c r="J592" t="inlineStr"/>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (Vientre Ovino) (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0591-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0592-2026</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0592-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0593-2026</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+      <c r="J594" t="inlineStr"/>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>la Subsecretaria del Centro de Control, Comando, Comunicaciones, Cómputo, Coordinación, e Inteligencia de la Secretaría de Seguridad Pública del Poder Ejecutivo del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0593-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -27316,7 +27316,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr"/>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="M553" t="inlineStr">
         <is>
           <t>Equipamiento Especializado para la Elaboración y Supervisión de Proyectos</t>
@@ -27381,7 +27385,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L554" t="inlineStr"/>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="M554" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -27446,7 +27454,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr"/>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="M555" t="inlineStr">
         <is>
           <t>Utensilios para el Servicio de Alimentación</t>
@@ -27511,7 +27523,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L556" t="inlineStr"/>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="M556" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Cría de Trucha Arcoíris)</t>
@@ -27576,7 +27592,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr"/>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="M557" t="inlineStr">
         <is>
           <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O594"/>
+  <dimension ref="A1:O599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26840,7 +26840,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr">
         <is>
@@ -27656,7 +27660,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr"/>
       <c r="M558" t="inlineStr">
         <is>
@@ -27717,7 +27725,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr"/>
       <c r="M559" t="inlineStr">
         <is>
@@ -27847,7 +27859,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr"/>
       <c r="M561" t="inlineStr">
         <is>
@@ -27908,7 +27924,11 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr"/>
       <c r="M562" t="inlineStr">
         <is>
@@ -28578,7 +28598,11 @@
       </c>
       <c r="H573" t="inlineStr"/>
       <c r="I573" t="inlineStr"/>
-      <c r="J573" t="inlineStr"/>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K573" t="inlineStr"/>
       <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr">
@@ -28635,7 +28659,11 @@
       </c>
       <c r="H574" t="inlineStr"/>
       <c r="I574" t="inlineStr"/>
-      <c r="J574" t="inlineStr"/>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K574" t="inlineStr"/>
       <c r="L574" t="inlineStr"/>
       <c r="M574" t="inlineStr">
@@ -28692,7 +28720,11 @@
       </c>
       <c r="H575" t="inlineStr"/>
       <c r="I575" t="inlineStr"/>
-      <c r="J575" t="inlineStr"/>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K575" t="inlineStr"/>
       <c r="L575" t="inlineStr"/>
       <c r="M575" t="inlineStr">
@@ -28749,7 +28781,11 @@
       </c>
       <c r="H576" t="inlineStr"/>
       <c r="I576" t="inlineStr"/>
-      <c r="J576" t="inlineStr"/>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K576" t="inlineStr"/>
       <c r="L576" t="inlineStr"/>
       <c r="M576" t="inlineStr">
@@ -28806,7 +28842,11 @@
       </c>
       <c r="H577" t="inlineStr"/>
       <c r="I577" t="inlineStr"/>
-      <c r="J577" t="inlineStr"/>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K577" t="inlineStr"/>
       <c r="L577" t="inlineStr"/>
       <c r="M577" t="inlineStr">
@@ -28863,7 +28903,11 @@
       </c>
       <c r="H578" t="inlineStr"/>
       <c r="I578" t="inlineStr"/>
-      <c r="J578" t="inlineStr"/>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K578" t="inlineStr"/>
       <c r="L578" t="inlineStr"/>
       <c r="M578" t="inlineStr">
@@ -28920,7 +28964,11 @@
       </c>
       <c r="H579" t="inlineStr"/>
       <c r="I579" t="inlineStr"/>
-      <c r="J579" t="inlineStr"/>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="K579" t="inlineStr"/>
       <c r="L579" t="inlineStr"/>
       <c r="M579" t="inlineStr">
@@ -29794,6 +29842,291 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0594-2026</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr"/>
+      <c r="J595" t="inlineStr"/>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>Material de Limpieza (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0594-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0595-2026</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr"/>
+      <c r="J596" t="inlineStr"/>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>del Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0595-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0596-2026</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+      <c r="J597" t="inlineStr"/>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0596-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0597-2026</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+      <c r="J598" t="inlineStr"/>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>Artículos Deportivos</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Prevención y Coordinación Institucional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0597-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0598-2026</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+      <c r="J599" t="inlineStr"/>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>Material Didáctico</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Prevención y Coordinación Institucional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0598-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O599"/>
+  <dimension ref="A1:O602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26845,7 +26845,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr"/>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="M546" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -27665,7 +27669,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr"/>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="M558" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Equipo de café) (Segundo Procedimiento)</t>
@@ -27864,7 +27872,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr"/>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="M561" t="inlineStr">
         <is>
           <t>Equipamiento Especializado para el Laboratorio de Turismo</t>
@@ -27989,7 +28001,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr">
         <is>
@@ -28050,7 +28066,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr">
         <is>
@@ -28111,7 +28131,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr">
         <is>
@@ -28172,7 +28196,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr"/>
       <c r="M566" t="inlineStr">
         <is>
@@ -28233,7 +28261,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr"/>
       <c r="M567" t="inlineStr">
         <is>
@@ -29025,7 +29057,11 @@
       </c>
       <c r="H580" t="inlineStr"/>
       <c r="I580" t="inlineStr"/>
-      <c r="J580" t="inlineStr"/>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K580" t="inlineStr"/>
       <c r="L580" t="inlineStr"/>
       <c r="M580" t="inlineStr">
@@ -29082,7 +29118,11 @@
       </c>
       <c r="H581" t="inlineStr"/>
       <c r="I581" t="inlineStr"/>
-      <c r="J581" t="inlineStr"/>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K581" t="inlineStr"/>
       <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr">
@@ -29139,7 +29179,11 @@
       </c>
       <c r="H582" t="inlineStr"/>
       <c r="I582" t="inlineStr"/>
-      <c r="J582" t="inlineStr"/>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K582" t="inlineStr"/>
       <c r="L582" t="inlineStr"/>
       <c r="M582" t="inlineStr">
@@ -29196,7 +29240,11 @@
       </c>
       <c r="H583" t="inlineStr"/>
       <c r="I583" t="inlineStr"/>
-      <c r="J583" t="inlineStr"/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K583" t="inlineStr"/>
       <c r="L583" t="inlineStr"/>
       <c r="M583" t="inlineStr">
@@ -29253,7 +29301,11 @@
       </c>
       <c r="H584" t="inlineStr"/>
       <c r="I584" t="inlineStr"/>
-      <c r="J584" t="inlineStr"/>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K584" t="inlineStr"/>
       <c r="L584" t="inlineStr"/>
       <c r="M584" t="inlineStr">
@@ -29310,7 +29362,11 @@
       </c>
       <c r="H585" t="inlineStr"/>
       <c r="I585" t="inlineStr"/>
-      <c r="J585" t="inlineStr"/>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K585" t="inlineStr"/>
       <c r="L585" t="inlineStr"/>
       <c r="M585" t="inlineStr">
@@ -29367,7 +29423,11 @@
       </c>
       <c r="H586" t="inlineStr"/>
       <c r="I586" t="inlineStr"/>
-      <c r="J586" t="inlineStr"/>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K586" t="inlineStr"/>
       <c r="L586" t="inlineStr"/>
       <c r="M586" t="inlineStr">
@@ -29424,7 +29484,11 @@
       </c>
       <c r="H587" t="inlineStr"/>
       <c r="I587" t="inlineStr"/>
-      <c r="J587" t="inlineStr"/>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K587" t="inlineStr"/>
       <c r="L587" t="inlineStr"/>
       <c r="M587" t="inlineStr">
@@ -29766,7 +29830,11 @@
       </c>
       <c r="H593" t="inlineStr"/>
       <c r="I593" t="inlineStr"/>
-      <c r="J593" t="inlineStr"/>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
       <c r="K593" t="inlineStr"/>
       <c r="L593" t="inlineStr"/>
       <c r="M593" t="inlineStr">
@@ -30127,6 +30195,177 @@
         </is>
       </c>
     </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0599-2026</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Servicio de Mantenimiento de Maquinaria y Equipo en Inmuebles (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>el Consejo Estatal para la Cultura y las Artes de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0599-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0600-2026</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>Equipamiento de la Orquesta Sinfónica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>la Dirección General de Vinculación, Programación y Difusión Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0600-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0601-2026</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>la División Científica de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0601-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O602"/>
+  <dimension ref="A1:O607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28006,7 +28006,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L563" t="inlineStr"/>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="M563" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información</t>
@@ -28071,7 +28075,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr"/>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="M564" t="inlineStr">
         <is>
           <t>Herramientas Menores</t>
@@ -28136,7 +28144,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr"/>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="M565" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -28201,7 +28213,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr"/>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="M566" t="inlineStr">
         <is>
           <t>Estudios e Investigaciones (Segundo Procedimiento)</t>
@@ -28266,7 +28282,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr"/>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="M567" t="inlineStr">
         <is>
           <t>Difusión de Programas y Actividades Gubernamentales</t>
@@ -28395,7 +28415,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr"/>
       <c r="M569" t="inlineStr">
         <is>
@@ -28452,7 +28476,11 @@
       <c r="H570" t="inlineStr"/>
       <c r="I570" t="inlineStr"/>
       <c r="J570" t="inlineStr"/>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr"/>
       <c r="M570" t="inlineStr">
         <is>
@@ -28513,7 +28541,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr"/>
       <c r="M571" t="inlineStr">
         <is>
@@ -28574,7 +28606,11 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr"/>
       <c r="M572" t="inlineStr">
         <is>
@@ -29545,7 +29581,11 @@
       </c>
       <c r="H588" t="inlineStr"/>
       <c r="I588" t="inlineStr"/>
-      <c r="J588" t="inlineStr"/>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K588" t="inlineStr"/>
       <c r="L588" t="inlineStr"/>
       <c r="M588" t="inlineStr">
@@ -29602,7 +29642,11 @@
       </c>
       <c r="H589" t="inlineStr"/>
       <c r="I589" t="inlineStr"/>
-      <c r="J589" t="inlineStr"/>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K589" t="inlineStr"/>
       <c r="L589" t="inlineStr"/>
       <c r="M589" t="inlineStr">
@@ -29659,7 +29703,11 @@
       </c>
       <c r="H590" t="inlineStr"/>
       <c r="I590" t="inlineStr"/>
-      <c r="J590" t="inlineStr"/>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K590" t="inlineStr"/>
       <c r="L590" t="inlineStr"/>
       <c r="M590" t="inlineStr">
@@ -29716,7 +29764,11 @@
       </c>
       <c r="H591" t="inlineStr"/>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr"/>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K591" t="inlineStr"/>
       <c r="L591" t="inlineStr"/>
       <c r="M591" t="inlineStr">
@@ -29773,7 +29825,11 @@
       </c>
       <c r="H592" t="inlineStr"/>
       <c r="I592" t="inlineStr"/>
-      <c r="J592" t="inlineStr"/>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K592" t="inlineStr"/>
       <c r="L592" t="inlineStr"/>
       <c r="M592" t="inlineStr">
@@ -29891,7 +29947,11 @@
       </c>
       <c r="H594" t="inlineStr"/>
       <c r="I594" t="inlineStr"/>
-      <c r="J594" t="inlineStr"/>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K594" t="inlineStr"/>
       <c r="L594" t="inlineStr"/>
       <c r="M594" t="inlineStr">
@@ -29948,7 +30008,11 @@
       </c>
       <c r="H595" t="inlineStr"/>
       <c r="I595" t="inlineStr"/>
-      <c r="J595" t="inlineStr"/>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
       <c r="K595" t="inlineStr"/>
       <c r="L595" t="inlineStr"/>
       <c r="M595" t="inlineStr">
@@ -30366,6 +30430,291 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0602-2026</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Materiales de Grabación, Muebles de Oficina y Estantería, Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N603" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0602-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0603-2026</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+      <c r="J604" t="inlineStr"/>
+      <c r="K604" t="inlineStr"/>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina, Estantería y Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N604" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0603-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0604-2026</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+      <c r="J605" t="inlineStr"/>
+      <c r="K605" t="inlineStr"/>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>Material Electrónico</t>
+        </is>
+      </c>
+      <c r="N605" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0604-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0605-2026</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr"/>
+      <c r="J606" t="inlineStr"/>
+      <c r="K606" t="inlineStr"/>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N606" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0605-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0606-2026</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+      <c r="J607" t="inlineStr"/>
+      <c r="K607" t="inlineStr"/>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N607" t="inlineStr">
+        <is>
+          <t>la Unidad de Recuperación de Vehículos de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0606-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O607"/>
+  <dimension ref="A1:O614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28481,7 +28481,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr"/>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="M570" t="inlineStr">
         <is>
           <t>Material Didáctico</t>
@@ -28546,7 +28550,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr"/>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="M571" t="inlineStr">
         <is>
           <t>Servicio Global para la Segunda Jornada Juvenil Cultural y Académica COBAEH 2026</t>
@@ -28611,7 +28619,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr"/>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="M572" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -28671,7 +28683,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr"/>
       <c r="M573" t="inlineStr">
         <is>
@@ -28732,7 +28748,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr"/>
       <c r="M574" t="inlineStr">
         <is>
@@ -28793,7 +28813,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr"/>
       <c r="M575" t="inlineStr">
         <is>
@@ -28854,7 +28878,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr"/>
       <c r="M576" t="inlineStr">
         <is>
@@ -28915,7 +28943,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr"/>
       <c r="M577" t="inlineStr">
         <is>
@@ -28976,7 +29008,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr"/>
       <c r="M578" t="inlineStr">
         <is>
@@ -29037,7 +29073,11 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr"/>
       <c r="M579" t="inlineStr">
         <is>
@@ -29891,8 +29931,16 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
-      <c r="L593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="M593" t="inlineStr">
         <is>
           <t>Servicios Integrales</t>
@@ -30069,7 +30117,11 @@
       </c>
       <c r="H596" t="inlineStr"/>
       <c r="I596" t="inlineStr"/>
-      <c r="J596" t="inlineStr"/>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K596" t="inlineStr"/>
       <c r="L596" t="inlineStr"/>
       <c r="M596" t="inlineStr">
@@ -30126,7 +30178,11 @@
       </c>
       <c r="H597" t="inlineStr"/>
       <c r="I597" t="inlineStr"/>
-      <c r="J597" t="inlineStr"/>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K597" t="inlineStr"/>
       <c r="L597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
@@ -30183,7 +30239,11 @@
       </c>
       <c r="H598" t="inlineStr"/>
       <c r="I598" t="inlineStr"/>
-      <c r="J598" t="inlineStr"/>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K598" t="inlineStr"/>
       <c r="L598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
@@ -30240,7 +30300,11 @@
       </c>
       <c r="H599" t="inlineStr"/>
       <c r="I599" t="inlineStr"/>
-      <c r="J599" t="inlineStr"/>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
       <c r="K599" t="inlineStr"/>
       <c r="L599" t="inlineStr"/>
       <c r="M599" t="inlineStr">
@@ -30715,6 +30779,405 @@
         </is>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0607-2026</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+      <c r="J608" t="inlineStr"/>
+      <c r="K608" t="inlineStr"/>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Muebles De Oficina, Estantería y Equipo de Administración, Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N608" t="inlineStr">
+        <is>
+          <t>la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0607-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0608-2026</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+      <c r="J609" t="inlineStr"/>
+      <c r="K609" t="inlineStr"/>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>Placas de Circulación Vehicular</t>
+        </is>
+      </c>
+      <c r="N609" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recaudación dependiente de la Subsecretaría de Ingresos de la Secretaría de Hacienda del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0608-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0609-2026</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+      <c r="J610" t="inlineStr"/>
+      <c r="K610" t="inlineStr"/>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Material de Oficina y Souvenirs</t>
+        </is>
+      </c>
+      <c r="N610" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0609-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0610-2026</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+      <c r="J611" t="inlineStr"/>
+      <c r="K611" t="inlineStr"/>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>Material Eléctrico</t>
+        </is>
+      </c>
+      <c r="N611" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Pachuca</t>
+        </is>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0610-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0611-2026</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr"/>
+      <c r="J612" t="inlineStr"/>
+      <c r="K612" t="inlineStr"/>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>Equipamiento de la Estación de Ferrocarril “Animas”</t>
+        </is>
+      </c>
+      <c r="N612" t="inlineStr">
+        <is>
+          <t>la Dirección General de Patrimonio Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0611-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0612-2026</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr"/>
+      <c r="J613" t="inlineStr"/>
+      <c r="K613" t="inlineStr"/>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>Sistemas de Aire Acondicionado, Calefacción y de Refrigeración Industrial y Comercial</t>
+        </is>
+      </c>
+      <c r="N613" t="inlineStr">
+        <is>
+          <t>la Dirección General de Vinculación, Programación y Difusión Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0612-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0613-2026</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N614" t="inlineStr">
+        <is>
+          <t>la Dirección General de Innovación Gubernamental de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0613-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O614"/>
+  <dimension ref="A1:O624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28688,7 +28688,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr"/>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M573" t="inlineStr">
         <is>
           <t>Mobiliario y Equipamiento de Oficina (Segundo Procedimiento)</t>
@@ -28753,7 +28757,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr"/>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M574" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -28883,7 +28891,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr"/>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M576" t="inlineStr">
         <is>
           <t>Muebles de Oficina y Estantería, Equipo de Administración</t>
@@ -28948,7 +28960,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr"/>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M577" t="inlineStr">
         <is>
           <t>Servicios de Informática</t>
@@ -29013,7 +29029,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr"/>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M578" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -29078,7 +29098,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr"/>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="M579" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -29138,7 +29162,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr"/>
       <c r="M580" t="inlineStr">
         <is>
@@ -29199,7 +29227,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr"/>
       <c r="M581" t="inlineStr">
         <is>
@@ -29260,7 +29292,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr"/>
       <c r="M582" t="inlineStr">
         <is>
@@ -29321,7 +29357,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr"/>
       <c r="M583" t="inlineStr">
         <is>
@@ -29382,7 +29422,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr"/>
       <c r="M584" t="inlineStr">
         <is>
@@ -29443,7 +29487,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr"/>
       <c r="M585" t="inlineStr">
         <is>
@@ -29504,7 +29552,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr"/>
       <c r="M586" t="inlineStr">
         <is>
@@ -29565,7 +29617,11 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr"/>
       <c r="M587" t="inlineStr">
         <is>
@@ -30061,8 +30117,16 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
-      <c r="L595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="M595" t="inlineStr">
         <is>
           <t>Material de Limpieza (Segundo Procedimiento)</t>
@@ -30361,7 +30425,11 @@
       </c>
       <c r="H600" t="inlineStr"/>
       <c r="I600" t="inlineStr"/>
-      <c r="J600" t="inlineStr"/>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K600" t="inlineStr"/>
       <c r="L600" t="inlineStr"/>
       <c r="M600" t="inlineStr">
@@ -30418,7 +30486,11 @@
       </c>
       <c r="H601" t="inlineStr"/>
       <c r="I601" t="inlineStr"/>
-      <c r="J601" t="inlineStr"/>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K601" t="inlineStr"/>
       <c r="L601" t="inlineStr"/>
       <c r="M601" t="inlineStr">
@@ -30475,7 +30547,11 @@
       </c>
       <c r="H602" t="inlineStr"/>
       <c r="I602" t="inlineStr"/>
-      <c r="J602" t="inlineStr"/>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
       <c r="K602" t="inlineStr"/>
       <c r="L602" t="inlineStr"/>
       <c r="M602" t="inlineStr">
@@ -31178,6 +31254,576 @@
         </is>
       </c>
     </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0614-2026</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N615" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo en conjunto con la Secretaría de Seguridad Pública del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0614-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0615-2026</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr"/>
+      <c r="I616" t="inlineStr"/>
+      <c r="J616" t="inlineStr"/>
+      <c r="K616" t="inlineStr"/>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N616" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0615-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0616-2026</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr"/>
+      <c r="J617" t="inlineStr"/>
+      <c r="K617" t="inlineStr"/>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N617" t="inlineStr">
+        <is>
+          <t>el Centro de Conciliación Laboral del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0616-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0617-2026</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+      <c r="J618" t="inlineStr"/>
+      <c r="K618" t="inlineStr"/>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N618" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0617-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0618-2026</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
+      <c r="J619" t="inlineStr"/>
+      <c r="K619" t="inlineStr"/>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Maquinaria y Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N619" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0618-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0619-2026</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+      <c r="J620" t="inlineStr"/>
+      <c r="K620" t="inlineStr"/>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N620" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0619-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0620-2026</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr"/>
+      <c r="J621" t="inlineStr"/>
+      <c r="K621" t="inlineStr"/>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>Software y Servicios Integrales de Infraestructura de Cómputo</t>
+        </is>
+      </c>
+      <c r="N621" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0620-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0621-2026</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr"/>
+      <c r="J622" t="inlineStr"/>
+      <c r="K622" t="inlineStr"/>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N622" t="inlineStr">
+        <is>
+          <t>la Dirección General de Conservación de Carreteras Estatales de la Secretaría de Infraestructura Pública y Desarrollo Urbano Sostenible del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0621-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0622-2026</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
+      <c r="J623" t="inlineStr"/>
+      <c r="K623" t="inlineStr"/>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N623" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Naturales, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0622-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0623-2026</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
+      <c r="J624" t="inlineStr"/>
+      <c r="K624" t="inlineStr"/>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas, Gastos de Oficina</t>
+        </is>
+      </c>
+      <c r="N624" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Francisco I. Madero</t>
+        </is>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0623-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O624"/>
+  <dimension ref="A1:O631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29167,7 +29167,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr"/>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="M580" t="inlineStr">
         <is>
           <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (colchones)</t>
@@ -29297,7 +29301,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L582" t="inlineStr"/>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="M582" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -29362,7 +29370,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L583" t="inlineStr"/>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="M583" t="inlineStr">
         <is>
           <t>Estudios e Investigaciones</t>
@@ -29492,7 +29504,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L585" t="inlineStr"/>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="M585" t="inlineStr">
         <is>
           <t>Bienes Informáticos, Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
@@ -29682,7 +29698,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr"/>
       <c r="M588" t="inlineStr">
         <is>
@@ -29743,7 +29763,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr"/>
       <c r="M589" t="inlineStr">
         <is>
@@ -29804,7 +29828,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr"/>
       <c r="M590" t="inlineStr">
         <is>
@@ -29865,7 +29893,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr"/>
       <c r="M591" t="inlineStr">
         <is>
@@ -29926,7 +29958,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr"/>
       <c r="M592" t="inlineStr">
         <is>
@@ -30056,7 +30092,11 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr"/>
       <c r="M594" t="inlineStr">
         <is>
@@ -30608,7 +30648,11 @@
       </c>
       <c r="H603" t="inlineStr"/>
       <c r="I603" t="inlineStr"/>
-      <c r="J603" t="inlineStr"/>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="K603" t="inlineStr"/>
       <c r="L603" t="inlineStr"/>
       <c r="M603" t="inlineStr">
@@ -30665,7 +30709,11 @@
       </c>
       <c r="H604" t="inlineStr"/>
       <c r="I604" t="inlineStr"/>
-      <c r="J604" t="inlineStr"/>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="K604" t="inlineStr"/>
       <c r="L604" t="inlineStr"/>
       <c r="M604" t="inlineStr">
@@ -30722,7 +30770,11 @@
       </c>
       <c r="H605" t="inlineStr"/>
       <c r="I605" t="inlineStr"/>
-      <c r="J605" t="inlineStr"/>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="K605" t="inlineStr"/>
       <c r="L605" t="inlineStr"/>
       <c r="M605" t="inlineStr">
@@ -30779,7 +30831,11 @@
       </c>
       <c r="H606" t="inlineStr"/>
       <c r="I606" t="inlineStr"/>
-      <c r="J606" t="inlineStr"/>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="K606" t="inlineStr"/>
       <c r="L606" t="inlineStr"/>
       <c r="M606" t="inlineStr">
@@ -30836,7 +30892,11 @@
       </c>
       <c r="H607" t="inlineStr"/>
       <c r="I607" t="inlineStr"/>
-      <c r="J607" t="inlineStr"/>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="K607" t="inlineStr"/>
       <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr">
@@ -31824,6 +31884,405 @@
         </is>
       </c>
     </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0624-2026</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr"/>
+      <c r="I625" t="inlineStr"/>
+      <c r="J625" t="inlineStr"/>
+      <c r="K625" t="inlineStr"/>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N625" t="inlineStr">
+        <is>
+          <t>El Colegio del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0624-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0625-2026</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+      <c r="J626" t="inlineStr"/>
+      <c r="K626" t="inlineStr"/>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>Equipamiento para Centros Educativos</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>el Colegio de Bachilleres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0625-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0626-2026</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+      <c r="J627" t="inlineStr"/>
+      <c r="K627" t="inlineStr"/>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>Servicios Integrales y Otros Servicios</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>la Dirección de Nomina, Operación y Desarrollo de la Dirección General de Recursos Humanos de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0626-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0627-2026</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr"/>
+      <c r="J628" t="inlineStr"/>
+      <c r="K628" t="inlineStr"/>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>la Dirección General de Movilidad Sustentable de la Secretaría de Movilidad y Transporte del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0627-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0628-2026</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+      <c r="J629" t="inlineStr"/>
+      <c r="K629" t="inlineStr"/>
+      <c r="L629" t="inlineStr"/>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>Alimentación de Personas</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0628-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0629-2026</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
+      <c r="J630" t="inlineStr"/>
+      <c r="K630" t="inlineStr"/>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (areteo)</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0629-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0630-2026</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr"/>
+      <c r="I631" t="inlineStr"/>
+      <c r="J631" t="inlineStr"/>
+      <c r="K631" t="inlineStr"/>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>Equipamiento Especializado para el Laboratorio de Ciencias (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0630-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O631"/>
+  <dimension ref="A1:O636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29439,7 +29439,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L584" t="inlineStr"/>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="M584" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -29703,7 +29707,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="L588" t="inlineStr"/>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="M588" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -29768,7 +29776,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="L589" t="inlineStr"/>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="M589" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros Médicos (Segundo Procedimiento)</t>
@@ -30097,7 +30109,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="L594" t="inlineStr"/>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="M594" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -30223,7 +30239,7 @@
       <c r="I596" t="inlineStr"/>
       <c r="J596" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="K596" t="inlineStr"/>
@@ -30287,7 +30303,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
@@ -30348,7 +30368,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
         <is>
@@ -30409,7 +30433,11 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr"/>
       <c r="M599" t="inlineStr">
         <is>
@@ -30953,7 +30981,11 @@
       </c>
       <c r="H608" t="inlineStr"/>
       <c r="I608" t="inlineStr"/>
-      <c r="J608" t="inlineStr"/>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K608" t="inlineStr"/>
       <c r="L608" t="inlineStr"/>
       <c r="M608" t="inlineStr">
@@ -31010,7 +31042,11 @@
       </c>
       <c r="H609" t="inlineStr"/>
       <c r="I609" t="inlineStr"/>
-      <c r="J609" t="inlineStr"/>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K609" t="inlineStr"/>
       <c r="L609" t="inlineStr"/>
       <c r="M609" t="inlineStr">
@@ -31067,7 +31103,11 @@
       </c>
       <c r="H610" t="inlineStr"/>
       <c r="I610" t="inlineStr"/>
-      <c r="J610" t="inlineStr"/>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K610" t="inlineStr"/>
       <c r="L610" t="inlineStr"/>
       <c r="M610" t="inlineStr">
@@ -31124,7 +31164,11 @@
       </c>
       <c r="H611" t="inlineStr"/>
       <c r="I611" t="inlineStr"/>
-      <c r="J611" t="inlineStr"/>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K611" t="inlineStr"/>
       <c r="L611" t="inlineStr"/>
       <c r="M611" t="inlineStr">
@@ -31181,7 +31225,11 @@
       </c>
       <c r="H612" t="inlineStr"/>
       <c r="I612" t="inlineStr"/>
-      <c r="J612" t="inlineStr"/>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K612" t="inlineStr"/>
       <c r="L612" t="inlineStr"/>
       <c r="M612" t="inlineStr">
@@ -31238,7 +31286,11 @@
       </c>
       <c r="H613" t="inlineStr"/>
       <c r="I613" t="inlineStr"/>
-      <c r="J613" t="inlineStr"/>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K613" t="inlineStr"/>
       <c r="L613" t="inlineStr"/>
       <c r="M613" t="inlineStr">
@@ -31295,7 +31347,11 @@
       </c>
       <c r="H614" t="inlineStr"/>
       <c r="I614" t="inlineStr"/>
-      <c r="J614" t="inlineStr"/>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
       <c r="K614" t="inlineStr"/>
       <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr">
@@ -32283,6 +32339,291 @@
         </is>
       </c>
     </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0631-2026</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
+      <c r="J632" t="inlineStr"/>
+      <c r="K632" t="inlineStr"/>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>Formas Valoradas</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0631-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0632-2026</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr"/>
+      <c r="I633" t="inlineStr"/>
+      <c r="J633" t="inlineStr"/>
+      <c r="K633" t="inlineStr"/>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>Equipamiento de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0632-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0633-2026</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
+      <c r="J634" t="inlineStr"/>
+      <c r="K634" t="inlineStr"/>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Materiales, Útiles y Equipos Menores de Oficina</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0633-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0634-2026</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr"/>
+      <c r="I635" t="inlineStr"/>
+      <c r="J635" t="inlineStr"/>
+      <c r="K635" t="inlineStr"/>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Fibras Sintéticas, Hules, Plásticos y Derivados</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0634-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0635-2026</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
+      <c r="J636" t="inlineStr"/>
+      <c r="K636" t="inlineStr"/>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0635-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -29910,7 +29910,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr"/>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M591" t="inlineStr">
         <is>
           <t>Alimentación de Animales (Segundo Procedimiento)</t>
@@ -29975,7 +29979,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="L592" t="inlineStr"/>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M592" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Vientre Ovino) (Segundo Procedimiento)</t>
@@ -30308,7 +30316,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="L597" t="inlineStr"/>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M597" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -30373,7 +30385,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="L598" t="inlineStr"/>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M598" t="inlineStr">
         <is>
           <t>Artículos Deportivos</t>
@@ -30438,7 +30454,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="L599" t="inlineStr"/>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="M599" t="inlineStr">
         <is>
           <t>Material Didáctico</t>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O636"/>
+  <dimension ref="A1:O643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30518,7 +30518,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr"/>
       <c r="M600" t="inlineStr">
         <is>
@@ -30579,7 +30583,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr"/>
       <c r="M601" t="inlineStr">
         <is>
@@ -30640,7 +30648,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr"/>
       <c r="M602" t="inlineStr">
         <is>
@@ -31428,7 +31440,11 @@
       </c>
       <c r="H615" t="inlineStr"/>
       <c r="I615" t="inlineStr"/>
-      <c r="J615" t="inlineStr"/>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K615" t="inlineStr"/>
       <c r="L615" t="inlineStr"/>
       <c r="M615" t="inlineStr">
@@ -31485,7 +31501,11 @@
       </c>
       <c r="H616" t="inlineStr"/>
       <c r="I616" t="inlineStr"/>
-      <c r="J616" t="inlineStr"/>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K616" t="inlineStr"/>
       <c r="L616" t="inlineStr"/>
       <c r="M616" t="inlineStr">
@@ -31542,7 +31562,11 @@
       </c>
       <c r="H617" t="inlineStr"/>
       <c r="I617" t="inlineStr"/>
-      <c r="J617" t="inlineStr"/>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K617" t="inlineStr"/>
       <c r="L617" t="inlineStr"/>
       <c r="M617" t="inlineStr">
@@ -31599,7 +31623,11 @@
       </c>
       <c r="H618" t="inlineStr"/>
       <c r="I618" t="inlineStr"/>
-      <c r="J618" t="inlineStr"/>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K618" t="inlineStr"/>
       <c r="L618" t="inlineStr"/>
       <c r="M618" t="inlineStr">
@@ -31656,7 +31684,11 @@
       </c>
       <c r="H619" t="inlineStr"/>
       <c r="I619" t="inlineStr"/>
-      <c r="J619" t="inlineStr"/>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K619" t="inlineStr"/>
       <c r="L619" t="inlineStr"/>
       <c r="M619" t="inlineStr">
@@ -31713,7 +31745,11 @@
       </c>
       <c r="H620" t="inlineStr"/>
       <c r="I620" t="inlineStr"/>
-      <c r="J620" t="inlineStr"/>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K620" t="inlineStr"/>
       <c r="L620" t="inlineStr"/>
       <c r="M620" t="inlineStr">
@@ -31770,7 +31806,11 @@
       </c>
       <c r="H621" t="inlineStr"/>
       <c r="I621" t="inlineStr"/>
-      <c r="J621" t="inlineStr"/>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K621" t="inlineStr"/>
       <c r="L621" t="inlineStr"/>
       <c r="M621" t="inlineStr">
@@ -31827,7 +31867,11 @@
       </c>
       <c r="H622" t="inlineStr"/>
       <c r="I622" t="inlineStr"/>
-      <c r="J622" t="inlineStr"/>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K622" t="inlineStr"/>
       <c r="L622" t="inlineStr"/>
       <c r="M622" t="inlineStr">
@@ -31884,7 +31928,11 @@
       </c>
       <c r="H623" t="inlineStr"/>
       <c r="I623" t="inlineStr"/>
-      <c r="J623" t="inlineStr"/>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K623" t="inlineStr"/>
       <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr">
@@ -31941,7 +31989,11 @@
       </c>
       <c r="H624" t="inlineStr"/>
       <c r="I624" t="inlineStr"/>
-      <c r="J624" t="inlineStr"/>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
       <c r="K624" t="inlineStr"/>
       <c r="L624" t="inlineStr"/>
       <c r="M624" t="inlineStr">
@@ -32644,6 +32696,405 @@
         </is>
       </c>
     </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0636-2026</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+      <c r="J637" t="inlineStr"/>
+      <c r="K637" t="inlineStr"/>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0636-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0637-2026</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+      <c r="J638" t="inlineStr"/>
+      <c r="K638" t="inlineStr"/>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>Servicios de Digitalización</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0637-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0638-2026</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+      <c r="J639" t="inlineStr"/>
+      <c r="K639" t="inlineStr"/>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N639" t="inlineStr">
+        <is>
+          <t>el el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0638-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0639-2026</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+      <c r="J640" t="inlineStr"/>
+      <c r="K640" t="inlineStr"/>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>Horno de Convección</t>
+        </is>
+      </c>
+      <c r="N640" t="inlineStr">
+        <is>
+          <t>el Bachillerato del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0639-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0640-2026</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+      <c r="J641" t="inlineStr"/>
+      <c r="K641" t="inlineStr"/>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>Equipamiento de Taller de Electricidad</t>
+        </is>
+      </c>
+      <c r="N641" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0640-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0641-2026</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+      <c r="J642" t="inlineStr"/>
+      <c r="K642" t="inlineStr"/>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N642" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0641-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0642-2026</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+      <c r="J643" t="inlineStr"/>
+      <c r="K643" t="inlineStr"/>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N643" t="inlineStr">
+        <is>
+          <t>la Central Estatal de Información, Investigación e Inteligencia de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0642-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O643"/>
+  <dimension ref="A1:O649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29236,7 +29236,11 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr"/>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="M581" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Módulos de Invernadero) (Segundo Procedimiento)</t>
@@ -30653,7 +30657,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="L602" t="inlineStr"/>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="M602" t="inlineStr">
         <is>
           <t>Sustancias Químicas</t>
@@ -30713,7 +30721,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr"/>
       <c r="M603" t="inlineStr">
         <is>
@@ -30774,7 +30786,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr"/>
       <c r="M604" t="inlineStr">
         <is>
@@ -30835,7 +30851,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr"/>
       <c r="M605" t="inlineStr">
         <is>
@@ -30896,7 +30916,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr"/>
       <c r="M606" t="inlineStr">
         <is>
@@ -30957,7 +30981,11 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr"/>
       <c r="M607" t="inlineStr">
         <is>
@@ -32050,7 +32078,11 @@
       </c>
       <c r="H625" t="inlineStr"/>
       <c r="I625" t="inlineStr"/>
-      <c r="J625" t="inlineStr"/>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K625" t="inlineStr"/>
       <c r="L625" t="inlineStr"/>
       <c r="M625" t="inlineStr">
@@ -32107,7 +32139,11 @@
       </c>
       <c r="H626" t="inlineStr"/>
       <c r="I626" t="inlineStr"/>
-      <c r="J626" t="inlineStr"/>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K626" t="inlineStr"/>
       <c r="L626" t="inlineStr"/>
       <c r="M626" t="inlineStr">
@@ -32164,7 +32200,11 @@
       </c>
       <c r="H627" t="inlineStr"/>
       <c r="I627" t="inlineStr"/>
-      <c r="J627" t="inlineStr"/>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K627" t="inlineStr"/>
       <c r="L627" t="inlineStr"/>
       <c r="M627" t="inlineStr">
@@ -32221,7 +32261,11 @@
       </c>
       <c r="H628" t="inlineStr"/>
       <c r="I628" t="inlineStr"/>
-      <c r="J628" t="inlineStr"/>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K628" t="inlineStr"/>
       <c r="L628" t="inlineStr"/>
       <c r="M628" t="inlineStr">
@@ -32278,7 +32322,11 @@
       </c>
       <c r="H629" t="inlineStr"/>
       <c r="I629" t="inlineStr"/>
-      <c r="J629" t="inlineStr"/>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K629" t="inlineStr"/>
       <c r="L629" t="inlineStr"/>
       <c r="M629" t="inlineStr">
@@ -32335,7 +32383,11 @@
       </c>
       <c r="H630" t="inlineStr"/>
       <c r="I630" t="inlineStr"/>
-      <c r="J630" t="inlineStr"/>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K630" t="inlineStr"/>
       <c r="L630" t="inlineStr"/>
       <c r="M630" t="inlineStr">
@@ -32392,7 +32444,11 @@
       </c>
       <c r="H631" t="inlineStr"/>
       <c r="I631" t="inlineStr"/>
-      <c r="J631" t="inlineStr"/>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="K631" t="inlineStr"/>
       <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
@@ -33095,6 +33151,348 @@
         </is>
       </c>
     </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0643-2026</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+      <c r="J644" t="inlineStr"/>
+      <c r="K644" t="inlineStr"/>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>Mobiliario para el Bachillerato del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="N644" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0643-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0644-2026</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
+      <c r="J645" t="inlineStr"/>
+      <c r="K645" t="inlineStr"/>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>Seguros</t>
+        </is>
+      </c>
+      <c r="N645" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0644-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0645-2026</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+      <c r="J646" t="inlineStr"/>
+      <c r="K646" t="inlineStr"/>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N646" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0645-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0646-2026</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+      <c r="J647" t="inlineStr"/>
+      <c r="K647" t="inlineStr"/>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N647" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0646-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0647-2026</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+      <c r="J648" t="inlineStr"/>
+      <c r="K648" t="inlineStr"/>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N648" t="inlineStr">
+        <is>
+          <t>el Instituto de Vivienda, Desarrollo Urbano y Asentamientos Humanos</t>
+        </is>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0647-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0648-2026</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr"/>
+      <c r="J649" t="inlineStr"/>
+      <c r="K649" t="inlineStr"/>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>Artículos Metálicos para la Construcción</t>
+        </is>
+      </c>
+      <c r="N649" t="inlineStr">
+        <is>
+          <t>la Dirección General de Ganadería de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0648-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O649"/>
+  <dimension ref="A1:O656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16121,7 +16121,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -30254,7 +30254,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr"/>
       <c r="M596" t="inlineStr">
         <is>
@@ -30791,7 +30795,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="L604" t="inlineStr"/>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="M604" t="inlineStr">
         <is>
           <t>Muebles de Oficina, Estantería y Equipo de Administración</t>
@@ -30856,7 +30864,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr"/>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="M605" t="inlineStr">
         <is>
           <t>Material Electrónico</t>
@@ -30921,7 +30933,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr"/>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="M606" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -30986,7 +31002,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="L607" t="inlineStr"/>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="M607" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -31046,7 +31066,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr"/>
       <c r="M608" t="inlineStr">
         <is>
@@ -31107,7 +31131,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr"/>
       <c r="M609" t="inlineStr">
         <is>
@@ -31168,7 +31196,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr"/>
       <c r="M610" t="inlineStr">
         <is>
@@ -31229,7 +31261,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr"/>
       <c r="M611" t="inlineStr">
         <is>
@@ -31290,7 +31326,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr"/>
       <c r="M612" t="inlineStr">
         <is>
@@ -31348,7 +31388,7 @@
       <c r="I613" t="inlineStr"/>
       <c r="J613" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="K613" t="inlineStr"/>
@@ -31412,7 +31452,11 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr"/>
       <c r="M614" t="inlineStr">
         <is>
@@ -32505,7 +32549,11 @@
       </c>
       <c r="H632" t="inlineStr"/>
       <c r="I632" t="inlineStr"/>
-      <c r="J632" t="inlineStr"/>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K632" t="inlineStr"/>
       <c r="L632" t="inlineStr"/>
       <c r="M632" t="inlineStr">
@@ -32562,7 +32610,11 @@
       </c>
       <c r="H633" t="inlineStr"/>
       <c r="I633" t="inlineStr"/>
-      <c r="J633" t="inlineStr"/>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K633" t="inlineStr"/>
       <c r="L633" t="inlineStr"/>
       <c r="M633" t="inlineStr">
@@ -32619,7 +32671,11 @@
       </c>
       <c r="H634" t="inlineStr"/>
       <c r="I634" t="inlineStr"/>
-      <c r="J634" t="inlineStr"/>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K634" t="inlineStr"/>
       <c r="L634" t="inlineStr"/>
       <c r="M634" t="inlineStr">
@@ -32676,7 +32732,11 @@
       </c>
       <c r="H635" t="inlineStr"/>
       <c r="I635" t="inlineStr"/>
-      <c r="J635" t="inlineStr"/>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr"/>
       <c r="M635" t="inlineStr">
@@ -32733,7 +32793,11 @@
       </c>
       <c r="H636" t="inlineStr"/>
       <c r="I636" t="inlineStr"/>
-      <c r="J636" t="inlineStr"/>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="K636" t="inlineStr"/>
       <c r="L636" t="inlineStr"/>
       <c r="M636" t="inlineStr">
@@ -33493,6 +33557,405 @@
         </is>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0649-2026</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>Equipo Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N650" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0649-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0650-2026</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0650-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0651-2026</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>Subsidios a la Producción (yeso agrícola, consorcio de bacterias y hongos)</t>
+        </is>
+      </c>
+      <c r="N652" t="inlineStr">
+        <is>
+          <t>la Dirección General de Agricultura de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0651-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0652-2026</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+      <c r="J653" t="inlineStr"/>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0652-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0653-2026</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+      <c r="J654" t="inlineStr"/>
+      <c r="K654" t="inlineStr"/>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>Aseguramiento de la Infraestructura Pública</t>
+        </is>
+      </c>
+      <c r="N654" t="inlineStr">
+        <is>
+          <t>el Sistema Integrado de Transporte Masivo de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0653-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0654-2026</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+      <c r="J655" t="inlineStr"/>
+      <c r="K655" t="inlineStr"/>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Identificadores e Iconos de Señalización</t>
+        </is>
+      </c>
+      <c r="N655" t="inlineStr">
+        <is>
+          <t>la Dirección de Infraestructura y Fomento Turístico dependiente de la Subsecretaría de Turismo de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0654-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0655-2026</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr"/>
+      <c r="J656" t="inlineStr"/>
+      <c r="K656" t="inlineStr"/>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Maquinaria y Equipo de Seguridad Pública</t>
+        </is>
+      </c>
+      <c r="N656" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0655-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O656"/>
+  <dimension ref="A1:O662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30259,7 +30259,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L596" t="inlineStr"/>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M596" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -31071,7 +31075,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L608" t="inlineStr"/>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M608" t="inlineStr">
         <is>
           <t>Muebles De Oficina, Estantería y Equipo de Administración, Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Otros Equipos</t>
@@ -31136,7 +31144,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L609" t="inlineStr"/>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M609" t="inlineStr">
         <is>
           <t>Placas de Circulación Vehicular</t>
@@ -31201,7 +31213,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L610" t="inlineStr"/>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M610" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Material de Oficina y Souvenirs</t>
@@ -31266,7 +31282,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L611" t="inlineStr"/>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M611" t="inlineStr">
         <is>
           <t>Material Eléctrico</t>
@@ -31457,7 +31477,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="L614" t="inlineStr"/>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="M614" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -31517,7 +31541,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr"/>
       <c r="M615" t="inlineStr">
         <is>
@@ -31578,7 +31606,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr"/>
       <c r="M616" t="inlineStr">
         <is>
@@ -31639,7 +31671,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr"/>
       <c r="M617" t="inlineStr">
         <is>
@@ -31700,7 +31736,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr"/>
       <c r="M618" t="inlineStr">
         <is>
@@ -31761,7 +31801,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr"/>
       <c r="M619" t="inlineStr">
         <is>
@@ -31822,7 +31866,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr"/>
       <c r="M620" t="inlineStr">
         <is>
@@ -31883,7 +31931,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr"/>
       <c r="M621" t="inlineStr">
         <is>
@@ -31944,7 +31996,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr"/>
       <c r="M622" t="inlineStr">
         <is>
@@ -32005,7 +32061,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr"/>
       <c r="M623" t="inlineStr">
         <is>
@@ -32066,7 +32126,11 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr"/>
       <c r="M624" t="inlineStr">
         <is>
@@ -32854,7 +32918,11 @@
       </c>
       <c r="H637" t="inlineStr"/>
       <c r="I637" t="inlineStr"/>
-      <c r="J637" t="inlineStr"/>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K637" t="inlineStr"/>
       <c r="L637" t="inlineStr"/>
       <c r="M637" t="inlineStr">
@@ -32911,7 +32979,11 @@
       </c>
       <c r="H638" t="inlineStr"/>
       <c r="I638" t="inlineStr"/>
-      <c r="J638" t="inlineStr"/>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K638" t="inlineStr"/>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr">
@@ -32968,7 +33040,11 @@
       </c>
       <c r="H639" t="inlineStr"/>
       <c r="I639" t="inlineStr"/>
-      <c r="J639" t="inlineStr"/>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K639" t="inlineStr"/>
       <c r="L639" t="inlineStr"/>
       <c r="M639" t="inlineStr">
@@ -33025,7 +33101,11 @@
       </c>
       <c r="H640" t="inlineStr"/>
       <c r="I640" t="inlineStr"/>
-      <c r="J640" t="inlineStr"/>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K640" t="inlineStr"/>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr">
@@ -33082,7 +33162,11 @@
       </c>
       <c r="H641" t="inlineStr"/>
       <c r="I641" t="inlineStr"/>
-      <c r="J641" t="inlineStr"/>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K641" t="inlineStr"/>
       <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr">
@@ -33139,7 +33223,11 @@
       </c>
       <c r="H642" t="inlineStr"/>
       <c r="I642" t="inlineStr"/>
-      <c r="J642" t="inlineStr"/>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K642" t="inlineStr"/>
       <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr">
@@ -33196,7 +33284,11 @@
       </c>
       <c r="H643" t="inlineStr"/>
       <c r="I643" t="inlineStr"/>
-      <c r="J643" t="inlineStr"/>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="K643" t="inlineStr"/>
       <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr">
@@ -33956,6 +34048,348 @@
         </is>
       </c>
     </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0656-2026</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+      <c r="J657" t="inlineStr"/>
+      <c r="K657" t="inlineStr"/>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N657" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de la Sierra Hidalguense</t>
+        </is>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0656-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0657-2026</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+      <c r="J658" t="inlineStr"/>
+      <c r="K658" t="inlineStr"/>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>Equipos y Aparatos Audiovisuales</t>
+        </is>
+      </c>
+      <c r="N658" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0657-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0658-2026</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+      <c r="J659" t="inlineStr"/>
+      <c r="K659" t="inlineStr"/>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N659" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0658-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0659-2026</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+      <c r="J660" t="inlineStr"/>
+      <c r="K660" t="inlineStr"/>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>Material Didáctico</t>
+        </is>
+      </c>
+      <c r="N660" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0659-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0660-2026</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr"/>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>Utensilios para el Servicio de Alimentación (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N661" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0660-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0661-2026</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr"/>
+      <c r="J662" t="inlineStr"/>
+      <c r="K662" t="inlineStr"/>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N662" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0661-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -23990,8 +23990,16 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
       <c r="M504" t="inlineStr">
         <is>
           <t>Servicios de Creatividad, Preproducción y Producción de Publicidad, Excepto Internet</t>
@@ -26427,10 +26435,14 @@
       <c r="I540" t="inlineStr"/>
       <c r="J540" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="K540" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
       <c r="L540" t="inlineStr">
         <is>
           <t>2026-09-11</t>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O662"/>
+  <dimension ref="A1:O668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16140,7 +16140,7 @@
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -31558,7 +31558,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L615" t="inlineStr"/>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M615" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -31623,7 +31627,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L616" t="inlineStr"/>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M616" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -31688,7 +31696,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L617" t="inlineStr"/>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M617" t="inlineStr">
         <is>
           <t>Material de Oficina</t>
@@ -31750,10 +31762,14 @@
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="L618" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M618" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -31818,7 +31834,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L619" t="inlineStr"/>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M619" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Maquinaria y Otros Equipos</t>
@@ -31948,7 +31968,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L621" t="inlineStr"/>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M621" t="inlineStr">
         <is>
           <t>Software y Servicios Integrales de Infraestructura de Cómputo</t>
@@ -32013,7 +32037,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L622" t="inlineStr"/>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M622" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación (Tercer Procedimiento)</t>
@@ -32078,7 +32106,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr"/>
+      <c r="L623" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="M623" t="inlineStr">
         <is>
           <t>Estudios e Investigaciones (Tercer Procedimiento)</t>
@@ -32203,7 +32235,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr"/>
       <c r="M625" t="inlineStr">
         <is>
@@ -32264,7 +32300,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr"/>
       <c r="M626" t="inlineStr">
         <is>
@@ -32325,7 +32365,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr"/>
       <c r="M627" t="inlineStr">
         <is>
@@ -32386,7 +32430,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr"/>
       <c r="M628" t="inlineStr">
         <is>
@@ -32447,7 +32495,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr"/>
       <c r="M629" t="inlineStr">
         <is>
@@ -32508,7 +32560,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr"/>
       <c r="M630" t="inlineStr">
         <is>
@@ -32569,7 +32625,11 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr"/>
       <c r="M631" t="inlineStr">
         <is>
@@ -33357,7 +33417,11 @@
       </c>
       <c r="H644" t="inlineStr"/>
       <c r="I644" t="inlineStr"/>
-      <c r="J644" t="inlineStr"/>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K644" t="inlineStr"/>
       <c r="L644" t="inlineStr"/>
       <c r="M644" t="inlineStr">
@@ -33414,7 +33478,11 @@
       </c>
       <c r="H645" t="inlineStr"/>
       <c r="I645" t="inlineStr"/>
-      <c r="J645" t="inlineStr"/>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K645" t="inlineStr"/>
       <c r="L645" t="inlineStr"/>
       <c r="M645" t="inlineStr">
@@ -33471,7 +33539,11 @@
       </c>
       <c r="H646" t="inlineStr"/>
       <c r="I646" t="inlineStr"/>
-      <c r="J646" t="inlineStr"/>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K646" t="inlineStr"/>
       <c r="L646" t="inlineStr"/>
       <c r="M646" t="inlineStr">
@@ -33528,7 +33600,11 @@
       </c>
       <c r="H647" t="inlineStr"/>
       <c r="I647" t="inlineStr"/>
-      <c r="J647" t="inlineStr"/>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K647" t="inlineStr"/>
       <c r="L647" t="inlineStr"/>
       <c r="M647" t="inlineStr">
@@ -33585,7 +33661,11 @@
       </c>
       <c r="H648" t="inlineStr"/>
       <c r="I648" t="inlineStr"/>
-      <c r="J648" t="inlineStr"/>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K648" t="inlineStr"/>
       <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr">
@@ -33642,7 +33722,11 @@
       </c>
       <c r="H649" t="inlineStr"/>
       <c r="I649" t="inlineStr"/>
-      <c r="J649" t="inlineStr"/>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="K649" t="inlineStr"/>
       <c r="L649" t="inlineStr"/>
       <c r="M649" t="inlineStr">
@@ -34402,6 +34486,348 @@
         </is>
       </c>
     </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0662-2026</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+      <c r="J663" t="inlineStr"/>
+      <c r="K663" t="inlineStr"/>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>Arrendamiento de Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N663" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0662-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0663-2026</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr"/>
+      <c r="J664" t="inlineStr"/>
+      <c r="K664" t="inlineStr"/>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>Servicios de Informática</t>
+        </is>
+      </c>
+      <c r="N664" t="inlineStr">
+        <is>
+          <t>la Dirección General de Monitoreo en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0663-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0664-2026</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+      <c r="J665" t="inlineStr"/>
+      <c r="K665" t="inlineStr"/>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N665" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0664-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0665-2026</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+      <c r="J666" t="inlineStr"/>
+      <c r="K666" t="inlineStr"/>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina, Estantería y Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N666" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0665-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0666-2026</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr"/>
+      <c r="J667" t="inlineStr"/>
+      <c r="K667" t="inlineStr"/>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N667" t="inlineStr">
+        <is>
+          <t>la Dirección General de Monitoreo en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0666-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0667-2026</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr"/>
+      <c r="J668" t="inlineStr"/>
+      <c r="K668" t="inlineStr"/>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N668" t="inlineStr">
+        <is>
+          <t>la Dirección General de Monitoreo en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0667-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O668"/>
+  <dimension ref="A1:O675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13564,7 +13564,7 @@
       <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="L390" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M390" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M392" t="inlineStr">
@@ -17644,7 +17644,7 @@
       </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -17980,7 +17980,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L416" t="inlineStr">
@@ -19952,7 +19952,7 @@
       <c r="I445" t="inlineStr"/>
       <c r="J445" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
@@ -20095,12 +20095,12 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="L447" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M447" t="inlineStr">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="M460" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="L485" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="M485" t="inlineStr">
@@ -23504,7 +23504,7 @@
       <c r="I497" t="inlineStr"/>
       <c r="J497" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="K497" t="inlineStr">
@@ -25481,7 +25481,7 @@
       <c r="I526" t="inlineStr"/>
       <c r="J526" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
@@ -25619,7 +25619,7 @@
       <c r="I528" t="inlineStr"/>
       <c r="J528" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
@@ -25688,7 +25688,7 @@
       <c r="I529" t="inlineStr"/>
       <c r="J529" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="K529" t="inlineStr">
@@ -31423,7 +31423,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr"/>
       <c r="M613" t="inlineStr">
         <is>
@@ -32240,7 +32244,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="L625" t="inlineStr"/>
+      <c r="L625" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="M625" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -32305,7 +32313,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="L626" t="inlineStr"/>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="M626" t="inlineStr">
         <is>
           <t>Equipamiento para Centros Educativos</t>
@@ -32362,7 +32374,7 @@
       <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -32500,7 +32512,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="L629" t="inlineStr"/>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="M629" t="inlineStr">
         <is>
           <t>Alimentación de Personas</t>
@@ -32565,7 +32581,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="L630" t="inlineStr"/>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="M630" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (areteo)</t>
@@ -32690,7 +32710,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr"/>
       <c r="M632" t="inlineStr">
         <is>
@@ -32751,7 +32775,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr"/>
       <c r="M633" t="inlineStr">
         <is>
@@ -32812,7 +32840,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr"/>
       <c r="M634" t="inlineStr">
         <is>
@@ -32873,7 +32905,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr"/>
       <c r="M635" t="inlineStr">
         <is>
@@ -32934,7 +32970,11 @@
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr"/>
       <c r="M636" t="inlineStr">
         <is>
@@ -33783,7 +33823,11 @@
       </c>
       <c r="H650" t="inlineStr"/>
       <c r="I650" t="inlineStr"/>
-      <c r="J650" t="inlineStr"/>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K650" t="inlineStr"/>
       <c r="L650" t="inlineStr"/>
       <c r="M650" t="inlineStr">
@@ -33840,7 +33884,11 @@
       </c>
       <c r="H651" t="inlineStr"/>
       <c r="I651" t="inlineStr"/>
-      <c r="J651" t="inlineStr"/>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K651" t="inlineStr"/>
       <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr">
@@ -33897,7 +33945,11 @@
       </c>
       <c r="H652" t="inlineStr"/>
       <c r="I652" t="inlineStr"/>
-      <c r="J652" t="inlineStr"/>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
@@ -33954,7 +34006,11 @@
       </c>
       <c r="H653" t="inlineStr"/>
       <c r="I653" t="inlineStr"/>
-      <c r="J653" t="inlineStr"/>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K653" t="inlineStr"/>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr">
@@ -34011,7 +34067,11 @@
       </c>
       <c r="H654" t="inlineStr"/>
       <c r="I654" t="inlineStr"/>
-      <c r="J654" t="inlineStr"/>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K654" t="inlineStr"/>
       <c r="L654" t="inlineStr"/>
       <c r="M654" t="inlineStr">
@@ -34068,7 +34128,11 @@
       </c>
       <c r="H655" t="inlineStr"/>
       <c r="I655" t="inlineStr"/>
-      <c r="J655" t="inlineStr"/>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K655" t="inlineStr"/>
       <c r="L655" t="inlineStr"/>
       <c r="M655" t="inlineStr">
@@ -34125,7 +34189,11 @@
       </c>
       <c r="H656" t="inlineStr"/>
       <c r="I656" t="inlineStr"/>
-      <c r="J656" t="inlineStr"/>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
       <c r="K656" t="inlineStr"/>
       <c r="L656" t="inlineStr"/>
       <c r="M656" t="inlineStr">
@@ -34828,6 +34896,405 @@
         </is>
       </c>
     </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0668-2026</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr"/>
+      <c r="J669" t="inlineStr"/>
+      <c r="K669" t="inlineStr"/>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>Servicios de Apoyo Administrativo, Fotocopiado e Impresión</t>
+        </is>
+      </c>
+      <c r="N669" t="inlineStr">
+        <is>
+          <t>el Despacho de la Persona Titular del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0668-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0669-2026</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+      <c r="J670" t="inlineStr"/>
+      <c r="K670" t="inlineStr"/>
+      <c r="L670" t="inlineStr"/>
+      <c r="M670" t="inlineStr">
+        <is>
+          <t>Material de Limpieza</t>
+        </is>
+      </c>
+      <c r="N670" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O670" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0669-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0670-2026</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr"/>
+      <c r="L671" t="inlineStr"/>
+      <c r="M671" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N671" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O671" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0670-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0671-2026</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+      <c r="J672" t="inlineStr"/>
+      <c r="K672" t="inlineStr"/>
+      <c r="L672" t="inlineStr"/>
+      <c r="M672" t="inlineStr">
+        <is>
+          <t>Herramientas y Máquinas-Herramienta</t>
+        </is>
+      </c>
+      <c r="N672" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O672" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0671-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0672-2026</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
+      <c r="J673" t="inlineStr"/>
+      <c r="K673" t="inlineStr"/>
+      <c r="L673" t="inlineStr"/>
+      <c r="M673" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N673" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Operación Policial de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O673" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0672-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0673-2026</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
+      <c r="J674" t="inlineStr"/>
+      <c r="K674" t="inlineStr"/>
+      <c r="L674" t="inlineStr"/>
+      <c r="M674" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N674" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O674" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0673-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0674-2026</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
+      <c r="J675" t="inlineStr"/>
+      <c r="K675" t="inlineStr"/>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N675" t="inlineStr">
+        <is>
+          <t>el Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0674-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -15746,7 +15746,11 @@
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="L379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
@@ -25152,7 +25156,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr"/>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M521" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (Vientre Ovino)</t>
@@ -27683,7 +27691,7 @@
       </c>
       <c r="L558" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="M558" t="inlineStr">
@@ -31428,7 +31436,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="L613" t="inlineStr"/>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M613" t="inlineStr">
         <is>
           <t>Sistemas de Aire Acondicionado, Calefacción y de Refrigeración Industrial y Comercial</t>
@@ -32374,7 +32386,7 @@
       <c r="I627" t="inlineStr"/>
       <c r="J627" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K627" t="inlineStr">
@@ -32382,7 +32394,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="L627" t="inlineStr"/>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M627" t="inlineStr">
         <is>
           <t>Servicios Integrales y Otros Servicios</t>
@@ -32715,7 +32731,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="L632" t="inlineStr"/>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M632" t="inlineStr">
         <is>
           <t>Formas Valoradas</t>
@@ -32910,7 +32930,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr"/>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M635" t="inlineStr">
         <is>
           <t>Fibras Sintéticas, Hules, Plásticos y Derivados</t>
@@ -32975,7 +32999,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="L636" t="inlineStr"/>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="M636" t="inlineStr">
         <is>
           <t>Vestuario y Uniformes</t>
@@ -33035,7 +33063,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr"/>
       <c r="M637" t="inlineStr">
         <is>
@@ -33096,7 +33128,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr"/>
       <c r="M638" t="inlineStr">
         <is>
@@ -33157,7 +33193,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr"/>
       <c r="M639" t="inlineStr">
         <is>
@@ -33218,7 +33258,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr"/>
       <c r="M640" t="inlineStr">
         <is>
@@ -33279,7 +33323,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr"/>
       <c r="M641" t="inlineStr">
         <is>
@@ -33340,7 +33388,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr"/>
       <c r="M642" t="inlineStr">
         <is>
@@ -33401,7 +33453,11 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr"/>
       <c r="M643" t="inlineStr">
         <is>
@@ -34339,7 +34395,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -34306,7 +34306,11 @@
       </c>
       <c r="H657" t="inlineStr"/>
       <c r="I657" t="inlineStr"/>
-      <c r="J657" t="inlineStr"/>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K657" t="inlineStr"/>
       <c r="L657" t="inlineStr"/>
       <c r="M657" t="inlineStr">
@@ -34363,7 +34367,11 @@
       </c>
       <c r="H658" t="inlineStr"/>
       <c r="I658" t="inlineStr"/>
-      <c r="J658" t="inlineStr"/>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K658" t="inlineStr"/>
       <c r="L658" t="inlineStr"/>
       <c r="M658" t="inlineStr">
@@ -34420,7 +34428,11 @@
       </c>
       <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr"/>
-      <c r="J659" t="inlineStr"/>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K659" t="inlineStr"/>
       <c r="L659" t="inlineStr"/>
       <c r="M659" t="inlineStr">
@@ -34477,7 +34489,11 @@
       </c>
       <c r="H660" t="inlineStr"/>
       <c r="I660" t="inlineStr"/>
-      <c r="J660" t="inlineStr"/>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K660" t="inlineStr"/>
       <c r="L660" t="inlineStr"/>
       <c r="M660" t="inlineStr">
@@ -34534,7 +34550,11 @@
       </c>
       <c r="H661" t="inlineStr"/>
       <c r="I661" t="inlineStr"/>
-      <c r="J661" t="inlineStr"/>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K661" t="inlineStr"/>
       <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr">
@@ -34591,7 +34611,11 @@
       </c>
       <c r="H662" t="inlineStr"/>
       <c r="I662" t="inlineStr"/>
-      <c r="J662" t="inlineStr"/>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="K662" t="inlineStr"/>
       <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O675"/>
+  <dimension ref="A1:O680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35375,6 +35375,291 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0675-2026</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+      <c r="J676" t="inlineStr"/>
+      <c r="K676" t="inlineStr"/>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N676" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0675-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0676-2026</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+      <c r="J677" t="inlineStr"/>
+      <c r="K677" t="inlineStr"/>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N677" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0676-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0677-2026</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+      <c r="J678" t="inlineStr"/>
+      <c r="K678" t="inlineStr"/>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Asignaciones Presupuestarias al Poder Ejecutivo (Sombreros y Chalecos)</t>
+        </is>
+      </c>
+      <c r="N678" t="inlineStr">
+        <is>
+          <t>la Secretaría de Contraloría del Poder Ejecutivo del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0677-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0678-2026</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+      <c r="J679" t="inlineStr"/>
+      <c r="K679" t="inlineStr"/>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>Utensilios para el Servicio de Alimentación</t>
+        </is>
+      </c>
+      <c r="N679" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0678-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0679-2026</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr"/>
+      <c r="J680" t="inlineStr"/>
+      <c r="K680" t="inlineStr"/>
+      <c r="L680" t="inlineStr"/>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Donativos a Entes Públicos Estatales y Municipales</t>
+        </is>
+      </c>
+      <c r="N680" t="inlineStr">
+        <is>
+          <t>la Dirección de Alimentación y Desarrollo Comunitario del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0679-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O680"/>
+  <dimension ref="A1:O699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -29733,7 +29733,7 @@
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="M588" t="inlineStr">
@@ -33068,7 +33068,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="L637" t="inlineStr"/>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="M637" t="inlineStr">
         <is>
           <t>Muebles de Oficina y Estantería</t>
@@ -33133,7 +33137,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr"/>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="M638" t="inlineStr">
         <is>
           <t>Servicios de Digitalización</t>
@@ -33263,7 +33271,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr"/>
+      <c r="L640" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="M640" t="inlineStr">
         <is>
           <t>Horno de Convección</t>
@@ -33458,7 +33470,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr"/>
+      <c r="L643" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="M643" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -33518,8 +33534,16 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
-      <c r="L644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M644" t="inlineStr">
         <is>
           <t>Mobiliario para el Bachillerato del Estado de Hidalgo</t>
@@ -33579,8 +33603,16 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
-      <c r="L645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="M645" t="inlineStr">
         <is>
           <t>Seguros</t>
@@ -33640,8 +33672,16 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
-      <c r="L646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="M646" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -33701,8 +33741,16 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
-      <c r="L647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M647" t="inlineStr">
         <is>
           <t>Material de Oficina</t>
@@ -33762,7 +33810,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr"/>
       <c r="M648" t="inlineStr">
         <is>
@@ -33823,8 +33875,16 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
-      <c r="L649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="M649" t="inlineStr">
         <is>
           <t>Artículos Metálicos para la Construcción</t>
@@ -33884,7 +33944,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr"/>
       <c r="M650" t="inlineStr">
         <is>
@@ -33945,7 +34009,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr"/>
       <c r="M651" t="inlineStr">
         <is>
@@ -34006,7 +34074,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
@@ -34067,7 +34139,11 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr"/>
       <c r="M653" t="inlineStr">
         <is>
@@ -34128,8 +34204,16 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
-      <c r="L654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M654" t="inlineStr">
         <is>
           <t>Aseguramiento de la Infraestructura Pública</t>
@@ -34189,8 +34273,16 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
-      <c r="L655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M655" t="inlineStr">
         <is>
           <t>Identificadores e Iconos de Señalización</t>
@@ -34250,8 +34342,16 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
-      <c r="L656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M656" t="inlineStr">
         <is>
           <t>Maquinaria y Equipo de Seguridad Pública</t>
@@ -34311,7 +34411,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr"/>
       <c r="M657" t="inlineStr">
         <is>
@@ -34372,7 +34476,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr"/>
       <c r="M658" t="inlineStr">
         <is>
@@ -34433,7 +34541,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr"/>
       <c r="M659" t="inlineStr">
         <is>
@@ -34494,7 +34606,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr"/>
       <c r="M660" t="inlineStr">
         <is>
@@ -34555,7 +34671,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr"/>
       <c r="M661" t="inlineStr">
         <is>
@@ -34616,7 +34736,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr"/>
       <c r="M662" t="inlineStr">
         <is>
@@ -34672,7 +34796,11 @@
       </c>
       <c r="H663" t="inlineStr"/>
       <c r="I663" t="inlineStr"/>
-      <c r="J663" t="inlineStr"/>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K663" t="inlineStr"/>
       <c r="L663" t="inlineStr"/>
       <c r="M663" t="inlineStr">
@@ -34729,7 +34857,11 @@
       </c>
       <c r="H664" t="inlineStr"/>
       <c r="I664" t="inlineStr"/>
-      <c r="J664" t="inlineStr"/>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K664" t="inlineStr"/>
       <c r="L664" t="inlineStr"/>
       <c r="M664" t="inlineStr">
@@ -34786,7 +34918,11 @@
       </c>
       <c r="H665" t="inlineStr"/>
       <c r="I665" t="inlineStr"/>
-      <c r="J665" t="inlineStr"/>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K665" t="inlineStr"/>
       <c r="L665" t="inlineStr"/>
       <c r="M665" t="inlineStr">
@@ -34843,7 +34979,11 @@
       </c>
       <c r="H666" t="inlineStr"/>
       <c r="I666" t="inlineStr"/>
-      <c r="J666" t="inlineStr"/>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K666" t="inlineStr"/>
       <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr">
@@ -34900,7 +35040,11 @@
       </c>
       <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr"/>
-      <c r="J667" t="inlineStr"/>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="K667" t="inlineStr"/>
       <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr">
@@ -34958,7 +35102,11 @@
       <c r="H668" t="inlineStr"/>
       <c r="I668" t="inlineStr"/>
       <c r="J668" t="inlineStr"/>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr"/>
       <c r="M668" t="inlineStr">
         <is>
@@ -35014,9 +35162,21 @@
       </c>
       <c r="H669" t="inlineStr"/>
       <c r="I669" t="inlineStr"/>
-      <c r="J669" t="inlineStr"/>
-      <c r="K669" t="inlineStr"/>
-      <c r="L669" t="inlineStr"/>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="M669" t="inlineStr">
         <is>
           <t>Servicios de Apoyo Administrativo, Fotocopiado e Impresión</t>
@@ -35071,7 +35231,11 @@
       </c>
       <c r="H670" t="inlineStr"/>
       <c r="I670" t="inlineStr"/>
-      <c r="J670" t="inlineStr"/>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K670" t="inlineStr"/>
       <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr">
@@ -35128,7 +35292,11 @@
       </c>
       <c r="H671" t="inlineStr"/>
       <c r="I671" t="inlineStr"/>
-      <c r="J671" t="inlineStr"/>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K671" t="inlineStr"/>
       <c r="L671" t="inlineStr"/>
       <c r="M671" t="inlineStr">
@@ -35185,7 +35353,11 @@
       </c>
       <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr"/>
-      <c r="J672" t="inlineStr"/>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K672" t="inlineStr"/>
       <c r="L672" t="inlineStr"/>
       <c r="M672" t="inlineStr">
@@ -35242,7 +35414,11 @@
       </c>
       <c r="H673" t="inlineStr"/>
       <c r="I673" t="inlineStr"/>
-      <c r="J673" t="inlineStr"/>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K673" t="inlineStr"/>
       <c r="L673" t="inlineStr"/>
       <c r="M673" t="inlineStr">
@@ -35299,7 +35475,11 @@
       </c>
       <c r="H674" t="inlineStr"/>
       <c r="I674" t="inlineStr"/>
-      <c r="J674" t="inlineStr"/>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="K674" t="inlineStr"/>
       <c r="L674" t="inlineStr"/>
       <c r="M674" t="inlineStr">
@@ -35356,7 +35536,11 @@
       </c>
       <c r="H675" t="inlineStr"/>
       <c r="I675" t="inlineStr"/>
-      <c r="J675" t="inlineStr"/>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K675" t="inlineStr"/>
       <c r="L675" t="inlineStr"/>
       <c r="M675" t="inlineStr">
@@ -35413,7 +35597,11 @@
       </c>
       <c r="H676" t="inlineStr"/>
       <c r="I676" t="inlineStr"/>
-      <c r="J676" t="inlineStr"/>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K676" t="inlineStr"/>
       <c r="L676" t="inlineStr"/>
       <c r="M676" t="inlineStr">
@@ -35470,7 +35658,11 @@
       </c>
       <c r="H677" t="inlineStr"/>
       <c r="I677" t="inlineStr"/>
-      <c r="J677" t="inlineStr"/>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K677" t="inlineStr"/>
       <c r="L677" t="inlineStr"/>
       <c r="M677" t="inlineStr">
@@ -35527,7 +35719,11 @@
       </c>
       <c r="H678" t="inlineStr"/>
       <c r="I678" t="inlineStr"/>
-      <c r="J678" t="inlineStr"/>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K678" t="inlineStr"/>
       <c r="L678" t="inlineStr"/>
       <c r="M678" t="inlineStr">
@@ -35584,7 +35780,11 @@
       </c>
       <c r="H679" t="inlineStr"/>
       <c r="I679" t="inlineStr"/>
-      <c r="J679" t="inlineStr"/>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K679" t="inlineStr"/>
       <c r="L679" t="inlineStr"/>
       <c r="M679" t="inlineStr">
@@ -35641,7 +35841,11 @@
       </c>
       <c r="H680" t="inlineStr"/>
       <c r="I680" t="inlineStr"/>
-      <c r="J680" t="inlineStr"/>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="K680" t="inlineStr"/>
       <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr">
@@ -35657,6 +35861,1089 @@
       <c r="O680" t="inlineStr">
         <is>
           <t>pdfs/EA-913003989-N0679-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0680-2026</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr"/>
+      <c r="J681" t="inlineStr"/>
+      <c r="K681" t="inlineStr"/>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Asignación de combustible mediante monederos electrónicos</t>
+        </is>
+      </c>
+      <c r="N681" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal para el Desarrollo Sostenible de los Pueblos Indígenas</t>
+        </is>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0680-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0681-2026</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+      <c r="J682" t="inlineStr"/>
+      <c r="K682" t="inlineStr"/>
+      <c r="L682" t="inlineStr"/>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Equipo educativo para el Laboratorio de Innovación Agrícola Sustentable (Tercer Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N682" t="inlineStr">
+        <is>
+          <t>la Subdirección de Servicios Administrativos del Instituto Tecnológico Superior de Huichapan</t>
+        </is>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0681-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0682-2026</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+      <c r="J683" t="inlineStr"/>
+      <c r="K683" t="inlineStr"/>
+      <c r="L683" t="inlineStr"/>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Material Eléctrico</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Pachuca</t>
+        </is>
+      </c>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0682-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0683-2026</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
+      <c r="J684" t="inlineStr"/>
+      <c r="K684" t="inlineStr"/>
+      <c r="L684" t="inlineStr"/>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N684" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0683-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0684-2026</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
+      <c r="J685" t="inlineStr"/>
+      <c r="K685" t="inlineStr"/>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Materiales de Grabación, Muebles de Oficina y Estantería, Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
+        </is>
+      </c>
+      <c r="N685" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica Metropolitana de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0684-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0685-2026</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+      <c r="J686" t="inlineStr"/>
+      <c r="K686" t="inlineStr"/>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Equipamiento de la Estación de Ferrocarril “Animas”</t>
+        </is>
+      </c>
+      <c r="N686" t="inlineStr">
+        <is>
+          <t>la Dirección General de Patrimonio Cultural de la Secretaría de Cultura del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0685-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0686-2026</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+      <c r="J687" t="inlineStr"/>
+      <c r="K687" t="inlineStr"/>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N687" t="inlineStr">
+        <is>
+          <t>del Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0686-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0687-2026</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+      <c r="J688" t="inlineStr"/>
+      <c r="K688" t="inlineStr"/>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Equipamiento para Centros Educativos (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N688" t="inlineStr">
+        <is>
+          <t>el Colegio de Bachilleres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0687-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0688-2026</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+      <c r="J689" t="inlineStr"/>
+      <c r="K689" t="inlineStr"/>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N689" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0688-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0689-2026</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr"/>
+      <c r="J690" t="inlineStr"/>
+      <c r="K690" t="inlineStr"/>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N690" t="inlineStr">
+        <is>
+          <t>el Centro de Rehabilitación Integral Hidalgo y Centros de Rehabilitación Integral Regionales del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0689-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0690-2026</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr"/>
+      <c r="J691" t="inlineStr"/>
+      <c r="K691" t="inlineStr"/>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N691" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal de Vivienda</t>
+        </is>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0690-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0691-2026</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
+      <c r="J692" t="inlineStr"/>
+      <c r="K692" t="inlineStr"/>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Material de Oficina y Souvenirs (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N692" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0691-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0692-2026</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+      <c r="J693" t="inlineStr"/>
+      <c r="K693" t="inlineStr"/>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Formas Valoradas</t>
+        </is>
+      </c>
+      <c r="N693" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0692-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0693-2026</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+      <c r="J694" t="inlineStr"/>
+      <c r="K694" t="inlineStr"/>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Otros Equipos</t>
+        </is>
+      </c>
+      <c r="N694" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0693-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0694-2026</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr"/>
+      <c r="J695" t="inlineStr"/>
+      <c r="K695" t="inlineStr"/>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Equipamiento de Laboratorio (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N695" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0694-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0695-2026</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+      <c r="J696" t="inlineStr"/>
+      <c r="K696" t="inlineStr"/>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N696" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0695-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0696-2026</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+      <c r="J697" t="inlineStr"/>
+      <c r="K697" t="inlineStr"/>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N697" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal de Vivienda</t>
+        </is>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0696-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0697-2026</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+      <c r="J698" t="inlineStr"/>
+      <c r="K698" t="inlineStr"/>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores Otros Bienes Muebles</t>
+        </is>
+      </c>
+      <c r="N698" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0697-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0698-2026</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+      <c r="J699" t="inlineStr"/>
+      <c r="K699" t="inlineStr"/>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Edificios</t>
+        </is>
+      </c>
+      <c r="N699" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0698-2026.pdf</t>
         </is>
       </c>
     </row>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -33815,7 +33815,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr"/>
+      <c r="L648" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M648" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -34079,7 +34083,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="L652" t="inlineStr"/>
+      <c r="L652" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M652" t="inlineStr">
         <is>
           <t>Subsidios a la Producción (yeso agrícola, consorcio de bacterias y hongos)</t>
@@ -34416,7 +34424,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="L657" t="inlineStr"/>
+      <c r="L657" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M657" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -34481,7 +34493,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="L658" t="inlineStr"/>
+      <c r="L658" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M658" t="inlineStr">
         <is>
           <t>Equipos y Aparatos Audiovisuales</t>
@@ -34676,7 +34692,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr"/>
+      <c r="L661" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M661" t="inlineStr">
         <is>
           <t>Utensilios para el Servicio de Alimentación (Segundo Procedimiento)</t>
@@ -34741,7 +34761,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr"/>
+      <c r="L662" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="M662" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -34801,7 +34825,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr"/>
       <c r="M663" t="inlineStr">
         <is>
@@ -34862,7 +34890,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr"/>
       <c r="M664" t="inlineStr">
         <is>
@@ -34923,7 +34955,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr"/>
       <c r="M665" t="inlineStr">
         <is>
@@ -34984,7 +35020,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr"/>
       <c r="M666" t="inlineStr">
         <is>
@@ -35045,7 +35085,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr"/>
       <c r="M667" t="inlineStr">
         <is>
@@ -35104,7 +35148,7 @@
       <c r="J668" t="inlineStr"/>
       <c r="K668" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="L668" t="inlineStr"/>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O699"/>
+  <dimension ref="A1:O704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16144,7 +16144,7 @@
       <c r="I389" t="inlineStr"/>
       <c r="J389" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
@@ -26899,7 +26899,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -31815,7 +31815,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -35946,7 +35946,11 @@
       </c>
       <c r="H681" t="inlineStr"/>
       <c r="I681" t="inlineStr"/>
-      <c r="J681" t="inlineStr"/>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="K681" t="inlineStr"/>
       <c r="L681" t="inlineStr"/>
       <c r="M681" t="inlineStr">
@@ -36003,7 +36007,11 @@
       </c>
       <c r="H682" t="inlineStr"/>
       <c r="I682" t="inlineStr"/>
-      <c r="J682" t="inlineStr"/>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="K682" t="inlineStr"/>
       <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr">
@@ -36060,7 +36068,11 @@
       </c>
       <c r="H683" t="inlineStr"/>
       <c r="I683" t="inlineStr"/>
-      <c r="J683" t="inlineStr"/>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="K683" t="inlineStr"/>
       <c r="L683" t="inlineStr"/>
       <c r="M683" t="inlineStr">
@@ -36117,7 +36129,11 @@
       </c>
       <c r="H684" t="inlineStr"/>
       <c r="I684" t="inlineStr"/>
-      <c r="J684" t="inlineStr"/>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="K684" t="inlineStr"/>
       <c r="L684" t="inlineStr"/>
       <c r="M684" t="inlineStr">
@@ -36174,7 +36190,11 @@
       </c>
       <c r="H685" t="inlineStr"/>
       <c r="I685" t="inlineStr"/>
-      <c r="J685" t="inlineStr"/>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="K685" t="inlineStr"/>
       <c r="L685" t="inlineStr"/>
       <c r="M685" t="inlineStr">
@@ -36991,6 +37011,291 @@
         </is>
       </c>
     </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0699-2026</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+      <c r="J700" t="inlineStr"/>
+      <c r="K700" t="inlineStr"/>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Materiales, Accesorios y Suministros de Laboratorio</t>
+        </is>
+      </c>
+      <c r="N700" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0699-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0700-2026</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+      <c r="J701" t="inlineStr"/>
+      <c r="K701" t="inlineStr"/>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N701" t="inlineStr">
+        <is>
+          <t>la Escuela de Música del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0700-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0701-2026</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr"/>
+      <c r="J702" t="inlineStr"/>
+      <c r="K702" t="inlineStr"/>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Formas Valoradas</t>
+        </is>
+      </c>
+      <c r="N702" t="inlineStr">
+        <is>
+          <t>la Dirección General del Registro del Estado Familiar de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0701-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0702-2026</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+      <c r="J703" t="inlineStr"/>
+      <c r="K703" t="inlineStr"/>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N703" t="inlineStr">
+        <is>
+          <t>la División Científica de la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0702-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0703-2026</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+      <c r="J704" t="inlineStr"/>
+      <c r="K704" t="inlineStr"/>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N704" t="inlineStr">
+        <is>
+          <t>Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0703-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -36251,7 +36251,11 @@
       </c>
       <c r="H686" t="inlineStr"/>
       <c r="I686" t="inlineStr"/>
-      <c r="J686" t="inlineStr"/>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K686" t="inlineStr"/>
       <c r="L686" t="inlineStr"/>
       <c r="M686" t="inlineStr">
@@ -36308,7 +36312,11 @@
       </c>
       <c r="H687" t="inlineStr"/>
       <c r="I687" t="inlineStr"/>
-      <c r="J687" t="inlineStr"/>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K687" t="inlineStr"/>
       <c r="L687" t="inlineStr"/>
       <c r="M687" t="inlineStr">
@@ -36365,7 +36373,11 @@
       </c>
       <c r="H688" t="inlineStr"/>
       <c r="I688" t="inlineStr"/>
-      <c r="J688" t="inlineStr"/>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K688" t="inlineStr"/>
       <c r="L688" t="inlineStr"/>
       <c r="M688" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -33340,7 +33340,11 @@
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="L641" t="inlineStr"/>
+      <c r="L641" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M641" t="inlineStr">
         <is>
           <t>Equipamiento de Taller de Electricidad</t>
@@ -33953,7 +33957,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="L650" t="inlineStr"/>
+      <c r="L650" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M650" t="inlineStr">
         <is>
           <t>Equipo Médico y de Laboratorio</t>
@@ -34562,7 +34570,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="L659" t="inlineStr"/>
+      <c r="L659" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M659" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos (Segundo Procedimiento)</t>
@@ -34830,7 +34842,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr"/>
+      <c r="L663" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M663" t="inlineStr">
         <is>
           <t>Arrendamiento de Activos Intangibles</t>
@@ -34895,7 +34911,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr"/>
+      <c r="L664" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M664" t="inlineStr">
         <is>
           <t>Servicios de Informática</t>
@@ -35025,7 +35045,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L666" t="inlineStr"/>
+      <c r="L666" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M666" t="inlineStr">
         <is>
           <t>Muebles de Oficina, Estantería y Equipo de Administración</t>
@@ -35151,7 +35175,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L668" t="inlineStr"/>
+      <c r="L668" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="M668" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -35280,7 +35308,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr"/>
       <c r="M670" t="inlineStr">
         <is>
@@ -35341,7 +35373,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr"/>
       <c r="M671" t="inlineStr">
         <is>
@@ -35402,7 +35438,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr"/>
       <c r="M672" t="inlineStr">
         <is>
@@ -35463,7 +35503,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr"/>
       <c r="M673" t="inlineStr">
         <is>
@@ -35524,7 +35568,11 @@
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr"/>
       <c r="M674" t="inlineStr">
         <is>
@@ -35582,7 +35630,7 @@
       <c r="I675" t="inlineStr"/>
       <c r="J675" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="K675" t="inlineStr"/>
@@ -36491,7 +36539,11 @@
       </c>
       <c r="H690" t="inlineStr"/>
       <c r="I690" t="inlineStr"/>
-      <c r="J690" t="inlineStr"/>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K690" t="inlineStr"/>
       <c r="L690" t="inlineStr"/>
       <c r="M690" t="inlineStr">
@@ -36548,7 +36600,11 @@
       </c>
       <c r="H691" t="inlineStr"/>
       <c r="I691" t="inlineStr"/>
-      <c r="J691" t="inlineStr"/>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K691" t="inlineStr"/>
       <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr">
@@ -36605,7 +36661,11 @@
       </c>
       <c r="H692" t="inlineStr"/>
       <c r="I692" t="inlineStr"/>
-      <c r="J692" t="inlineStr"/>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K692" t="inlineStr"/>
       <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O704"/>
+  <dimension ref="A1:O709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36482,7 +36482,11 @@
       </c>
       <c r="H689" t="inlineStr"/>
       <c r="I689" t="inlineStr"/>
-      <c r="J689" t="inlineStr"/>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K689" t="inlineStr"/>
       <c r="L689" t="inlineStr"/>
       <c r="M689" t="inlineStr">
@@ -36722,7 +36726,11 @@
       </c>
       <c r="H693" t="inlineStr"/>
       <c r="I693" t="inlineStr"/>
-      <c r="J693" t="inlineStr"/>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K693" t="inlineStr"/>
       <c r="L693" t="inlineStr"/>
       <c r="M693" t="inlineStr">
@@ -36779,7 +36787,11 @@
       </c>
       <c r="H694" t="inlineStr"/>
       <c r="I694" t="inlineStr"/>
-      <c r="J694" t="inlineStr"/>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K694" t="inlineStr"/>
       <c r="L694" t="inlineStr"/>
       <c r="M694" t="inlineStr">
@@ -36836,7 +36848,11 @@
       </c>
       <c r="H695" t="inlineStr"/>
       <c r="I695" t="inlineStr"/>
-      <c r="J695" t="inlineStr"/>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="K695" t="inlineStr"/>
       <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr">
@@ -37368,6 +37384,275 @@
         </is>
       </c>
     </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0704-2026</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr"/>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+      <c r="J705" t="inlineStr"/>
+      <c r="K705" t="inlineStr"/>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Activos Intangibles (Sistema Integral de Enseñanza, Aprendizaje y Certificación del Idioma Inglés)</t>
+        </is>
+      </c>
+      <c r="N705" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo, por el Colegio de Estudios Científicos y Tecnológicos del Estado de Hidalgo, por el Colegio de Bachilleres del Estado de Hidalgo, y por el Bachillerato del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0704-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0705-2026</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+      <c r="J706" t="inlineStr"/>
+      <c r="K706" t="inlineStr"/>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N706" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0705-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0706-2026</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+      <c r="J707" t="inlineStr"/>
+      <c r="K707" t="inlineStr"/>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Bienes Informáticos, Equipos y Aparatos Audiovisuales, Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N707" t="inlineStr">
+        <is>
+          <t>la Dirección General de Gestión de Calidad del Aire, de la Secretaría de Medio Ambiente y Recursos Naturales del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0706-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0707-2026</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+      <c r="J708" t="inlineStr"/>
+      <c r="K708" t="inlineStr"/>
+      <c r="L708" t="inlineStr"/>
+      <c r="M708" t="inlineStr">
+        <is>
+          <t>Otros Equipos, Equipo Educacional y Recreativo</t>
+        </is>
+      </c>
+      <c r="N708" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O708" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0707-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0708-2026</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+      <c r="J709" t="inlineStr"/>
+      <c r="K709" t="inlineStr"/>
+      <c r="L709" t="inlineStr"/>
+      <c r="M709" t="inlineStr">
+        <is>
+          <t>Maquinaria y Equipo de Seguridad Pública (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N709" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O709" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0708-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -34980,7 +34980,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr"/>
+      <c r="L665" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M665" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -35114,7 +35118,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="L667" t="inlineStr"/>
+      <c r="L667" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M667" t="inlineStr">
         <is>
           <t>Activos Intangibles</t>
@@ -35313,7 +35321,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="L670" t="inlineStr"/>
+      <c r="L670" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M670" t="inlineStr">
         <is>
           <t>Material de Limpieza</t>
@@ -35378,7 +35390,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="L671" t="inlineStr"/>
+      <c r="L671" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M671" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -35508,7 +35524,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr"/>
+      <c r="L673" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M673" t="inlineStr">
         <is>
           <t>Material de Oficina</t>
@@ -35573,7 +35593,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr"/>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="M674" t="inlineStr">
         <is>
           <t>Material de Oficina</t>
@@ -35694,7 +35718,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr"/>
       <c r="M676" t="inlineStr">
         <is>
@@ -35755,7 +35783,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr"/>
       <c r="M677" t="inlineStr">
         <is>
@@ -35816,7 +35848,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr"/>
       <c r="M678" t="inlineStr">
         <is>
@@ -35877,7 +35913,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr"/>
       <c r="M679" t="inlineStr">
         <is>
@@ -35938,7 +35978,11 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr"/>
       <c r="M680" t="inlineStr">
         <is>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -36953,7 +36953,11 @@
       </c>
       <c r="H696" t="inlineStr"/>
       <c r="I696" t="inlineStr"/>
-      <c r="J696" t="inlineStr"/>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="K696" t="inlineStr"/>
       <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr">
@@ -37010,7 +37014,11 @@
       </c>
       <c r="H697" t="inlineStr"/>
       <c r="I697" t="inlineStr"/>
-      <c r="J697" t="inlineStr"/>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="K697" t="inlineStr"/>
       <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr">
@@ -37067,7 +37075,11 @@
       </c>
       <c r="H698" t="inlineStr"/>
       <c r="I698" t="inlineStr"/>
-      <c r="J698" t="inlineStr"/>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="K698" t="inlineStr"/>
       <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr">
@@ -37124,7 +37136,11 @@
       </c>
       <c r="H699" t="inlineStr"/>
       <c r="I699" t="inlineStr"/>
-      <c r="J699" t="inlineStr"/>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="K699" t="inlineStr"/>
       <c r="L699" t="inlineStr"/>
       <c r="M699" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -35723,7 +35723,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="L676" t="inlineStr"/>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M676" t="inlineStr">
         <is>
           <t>Equipos de Generación Eléctrica, Aparatos y Accesorios Eléctricos</t>
@@ -35788,7 +35792,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr"/>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M677" t="inlineStr">
         <is>
           <t>Material de Oficina</t>
@@ -35853,7 +35861,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="L678" t="inlineStr"/>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M678" t="inlineStr">
         <is>
           <t>Asignaciones Presupuestarias al Poder Ejecutivo (Sombreros y Chalecos)</t>
@@ -35918,7 +35930,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="L679" t="inlineStr"/>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M679" t="inlineStr">
         <is>
           <t>Utensilios para el Servicio de Alimentación</t>
@@ -35983,7 +35999,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="L680" t="inlineStr"/>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="M680" t="inlineStr">
         <is>
           <t>Donativos a Entes Públicos Estatales y Municipales</t>
@@ -36043,7 +36063,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr"/>
       <c r="M681" t="inlineStr">
         <is>
@@ -36104,7 +36128,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr"/>
       <c r="M682" t="inlineStr">
         <is>
@@ -36165,7 +36193,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr"/>
       <c r="M683" t="inlineStr">
         <is>
@@ -36226,7 +36258,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr"/>
       <c r="M684" t="inlineStr">
         <is>
@@ -36287,7 +36323,11 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr"/>
       <c r="M685" t="inlineStr">
         <is>
@@ -36348,7 +36388,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr"/>
       <c r="M686" t="inlineStr">
         <is>
@@ -36406,7 +36450,7 @@
       <c r="I687" t="inlineStr"/>
       <c r="J687" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="K687" t="inlineStr"/>
@@ -36470,7 +36514,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr"/>
       <c r="M688" t="inlineStr">
         <is>
@@ -37197,7 +37245,11 @@
       </c>
       <c r="H700" t="inlineStr"/>
       <c r="I700" t="inlineStr"/>
-      <c r="J700" t="inlineStr"/>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="K700" t="inlineStr"/>
       <c r="L700" t="inlineStr"/>
       <c r="M700" t="inlineStr">
@@ -37254,7 +37306,11 @@
       </c>
       <c r="H701" t="inlineStr"/>
       <c r="I701" t="inlineStr"/>
-      <c r="J701" t="inlineStr"/>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="K701" t="inlineStr"/>
       <c r="L701" t="inlineStr"/>
       <c r="M701" t="inlineStr">
@@ -37311,7 +37367,11 @@
       </c>
       <c r="H702" t="inlineStr"/>
       <c r="I702" t="inlineStr"/>
-      <c r="J702" t="inlineStr"/>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="K702" t="inlineStr"/>
       <c r="L702" t="inlineStr"/>
       <c r="M702" t="inlineStr">
@@ -37368,7 +37428,11 @@
       </c>
       <c r="H703" t="inlineStr"/>
       <c r="I703" t="inlineStr"/>
-      <c r="J703" t="inlineStr"/>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="K703" t="inlineStr"/>
       <c r="L703" t="inlineStr"/>
       <c r="M703" t="inlineStr">
@@ -37425,7 +37489,11 @@
       </c>
       <c r="H704" t="inlineStr"/>
       <c r="I704" t="inlineStr"/>
-      <c r="J704" t="inlineStr"/>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="K704" t="inlineStr"/>
       <c r="L704" t="inlineStr"/>
       <c r="M704" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O709"/>
+  <dimension ref="A1:O717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37781,6 +37781,462 @@
         </is>
       </c>
     </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0709-2026</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+      <c r="J710" t="inlineStr"/>
+      <c r="K710" t="inlineStr"/>
+      <c r="L710" t="inlineStr"/>
+      <c r="M710" t="inlineStr">
+        <is>
+          <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (colchones)</t>
+        </is>
+      </c>
+      <c r="N710" t="inlineStr">
+        <is>
+          <t>la Dirección General de Prevención y Reinserción Social de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O710" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0709-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0710-2026</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+      <c r="J711" t="inlineStr"/>
+      <c r="K711" t="inlineStr"/>
+      <c r="L711" t="inlineStr"/>
+      <c r="M711" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N711" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Protección Civil y Gestión de Riesgos de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O711" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0710-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0711-2026</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+      <c r="J712" t="inlineStr"/>
+      <c r="K712" t="inlineStr"/>
+      <c r="L712" t="inlineStr"/>
+      <c r="M712" t="inlineStr">
+        <is>
+          <t>Equipo para Laboratorio en Ciencias en Alimentos</t>
+        </is>
+      </c>
+      <c r="N712" t="inlineStr">
+        <is>
+          <t>el Instituto Tecnológico Superior del Oriente del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O712" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0711-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0712-2026</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
+      <c r="K713" t="inlineStr"/>
+      <c r="L713" t="inlineStr"/>
+      <c r="M713" t="inlineStr">
+        <is>
+          <t>Equipamiento para el fortalecimiento de la infraestructura educativa de la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="N713" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Tula Tepeji</t>
+        </is>
+      </c>
+      <c r="O713" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0712-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0713-2026</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+      <c r="J714" t="inlineStr"/>
+      <c r="K714" t="inlineStr"/>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos, Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O714" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0713-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0714-2026</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+      <c r="J715" t="inlineStr"/>
+      <c r="K715" t="inlineStr"/>
+      <c r="L715" t="inlineStr"/>
+      <c r="M715" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N715" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O715" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0714-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0715-2026</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>Maquinaria y Equipo Industrial</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Maquinaria para el Desarrollo</t>
+        </is>
+      </c>
+      <c r="O716" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0715-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0716-2026</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+      <c r="J717" t="inlineStr"/>
+      <c r="K717" t="inlineStr"/>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>Equipos y Aparatos de Audio</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr">
+        <is>
+          <t>el Colegio del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O717" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0716-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -35657,7 +35657,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr"/>
       <c r="M675" t="inlineStr">
         <is>
@@ -36068,7 +36072,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="L681" t="inlineStr"/>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="M681" t="inlineStr">
         <is>
           <t>Asignación de combustible mediante monederos electrónicos</t>
@@ -36198,7 +36206,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr"/>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="M683" t="inlineStr">
         <is>
           <t>Material Eléctrico</t>
@@ -36519,7 +36531,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="L688" t="inlineStr"/>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="M688" t="inlineStr">
         <is>
           <t>Equipamiento para Centros Educativos (Segundo Procedimiento)</t>
@@ -36579,7 +36595,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr"/>
       <c r="M689" t="inlineStr">
         <is>
@@ -36640,7 +36660,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr"/>
       <c r="M690" t="inlineStr">
         <is>
@@ -36701,7 +36725,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr"/>
       <c r="M691" t="inlineStr">
         <is>
@@ -36762,7 +36790,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr"/>
       <c r="M692" t="inlineStr">
         <is>
@@ -36823,7 +36855,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr"/>
       <c r="M693" t="inlineStr">
         <is>
@@ -36884,7 +36920,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr"/>
       <c r="M694" t="inlineStr">
         <is>
@@ -36945,7 +36985,11 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr"/>
       <c r="M695" t="inlineStr">
         <is>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O717"/>
+  <dimension ref="A1:O725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37578,7 +37578,11 @@
       <c r="G705" t="inlineStr"/>
       <c r="H705" t="inlineStr"/>
       <c r="I705" t="inlineStr"/>
-      <c r="J705" t="inlineStr"/>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="K705" t="inlineStr"/>
       <c r="L705" t="inlineStr"/>
       <c r="M705" t="inlineStr">
@@ -37635,7 +37639,11 @@
       </c>
       <c r="H706" t="inlineStr"/>
       <c r="I706" t="inlineStr"/>
-      <c r="J706" t="inlineStr"/>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="K706" t="inlineStr"/>
       <c r="L706" t="inlineStr"/>
       <c r="M706" t="inlineStr">
@@ -37692,7 +37700,11 @@
       </c>
       <c r="H707" t="inlineStr"/>
       <c r="I707" t="inlineStr"/>
-      <c r="J707" t="inlineStr"/>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="K707" t="inlineStr"/>
       <c r="L707" t="inlineStr"/>
       <c r="M707" t="inlineStr">
@@ -37749,7 +37761,11 @@
       </c>
       <c r="H708" t="inlineStr"/>
       <c r="I708" t="inlineStr"/>
-      <c r="J708" t="inlineStr"/>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="K708" t="inlineStr"/>
       <c r="L708" t="inlineStr"/>
       <c r="M708" t="inlineStr">
@@ -37806,7 +37822,11 @@
       </c>
       <c r="H709" t="inlineStr"/>
       <c r="I709" t="inlineStr"/>
-      <c r="J709" t="inlineStr"/>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
       <c r="K709" t="inlineStr"/>
       <c r="L709" t="inlineStr"/>
       <c r="M709" t="inlineStr">
@@ -38281,6 +38301,462 @@
         </is>
       </c>
     </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0717-2026</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="inlineStr"/>
+      <c r="L718" t="inlineStr"/>
+      <c r="M718" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N718" t="inlineStr">
+        <is>
+          <t>la Oficialía Mayor de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O718" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0717-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0718-2026</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+      <c r="J719" t="inlineStr"/>
+      <c r="K719" t="inlineStr"/>
+      <c r="L719" t="inlineStr"/>
+      <c r="M719" t="inlineStr">
+        <is>
+          <t>Silla y Mesa Escolar</t>
+        </is>
+      </c>
+      <c r="N719" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O719" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0718-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0719-2026</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+      <c r="J720" t="inlineStr"/>
+      <c r="K720" t="inlineStr"/>
+      <c r="L720" t="inlineStr"/>
+      <c r="M720" t="inlineStr">
+        <is>
+          <t>Mobiliario y Equipo de Aulas Didácticas</t>
+        </is>
+      </c>
+      <c r="N720" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O720" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0719-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0720-2026</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+      <c r="J721" t="inlineStr"/>
+      <c r="K721" t="inlineStr"/>
+      <c r="L721" t="inlineStr"/>
+      <c r="M721" t="inlineStr">
+        <is>
+          <t>Herramientas Menores</t>
+        </is>
+      </c>
+      <c r="N721" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O721" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0720-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0721-2026</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+      <c r="J722" t="inlineStr"/>
+      <c r="K722" t="inlineStr"/>
+      <c r="L722" t="inlineStr"/>
+      <c r="M722" t="inlineStr">
+        <is>
+          <t>Material de Oficina (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N722" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de Educación para Adultos</t>
+        </is>
+      </c>
+      <c r="O722" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0721-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0722-2026</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+      <c r="J723" t="inlineStr"/>
+      <c r="K723" t="inlineStr"/>
+      <c r="L723" t="inlineStr"/>
+      <c r="M723" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N723" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O723" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0722-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0723-2026</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+      <c r="J724" t="inlineStr"/>
+      <c r="K724" t="inlineStr"/>
+      <c r="L724" t="inlineStr"/>
+      <c r="M724" t="inlineStr">
+        <is>
+          <t>Mantenimiento de Maquinaria y Equipo</t>
+        </is>
+      </c>
+      <c r="N724" t="inlineStr">
+        <is>
+          <t>la Dirección General de Infraestructura y Maquinaria de la Secretaría de Agricultura y Desarrollo Rural del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O724" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0723-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0724-2026</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+      <c r="J725" t="inlineStr"/>
+      <c r="K725" t="inlineStr"/>
+      <c r="L725" t="inlineStr"/>
+      <c r="M725" t="inlineStr">
+        <is>
+          <t>Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N725" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O725" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0724-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -35662,7 +35662,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="L675" t="inlineStr"/>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="M675" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -36665,7 +36669,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="L690" t="inlineStr"/>
+      <c r="L690" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="M690" t="inlineStr">
         <is>
           <t>Instalación, Reparación y Mantenimiento de Equipo e Instrumental Médico y de Laboratorio</t>
@@ -36730,7 +36738,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="L691" t="inlineStr"/>
+      <c r="L691" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="M691" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -36795,7 +36807,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="L692" t="inlineStr"/>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="M692" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos, Refacciones y Accesorios Menores de Equipo de Cómputo y Tecnologías de la Información, Material de Oficina y Souvenirs (Segundo Procedimiento)</t>
@@ -36860,7 +36876,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="L693" t="inlineStr"/>
+      <c r="L693" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="M693" t="inlineStr">
         <is>
           <t>Formas Valoradas</t>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O725"/>
+  <dimension ref="A1:O727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37070,7 +37070,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr"/>
       <c r="M696" t="inlineStr">
         <is>
@@ -37131,7 +37135,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr"/>
       <c r="M697" t="inlineStr">
         <is>
@@ -37192,7 +37200,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr"/>
       <c r="M698" t="inlineStr">
         <is>
@@ -37253,7 +37265,11 @@
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr"/>
       <c r="M699" t="inlineStr">
         <is>
@@ -38777,6 +38793,120 @@
         </is>
       </c>
     </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0725-2026</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+      <c r="J726" t="inlineStr"/>
+      <c r="K726" t="inlineStr"/>
+      <c r="L726" t="inlineStr"/>
+      <c r="M726" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N726" t="inlineStr">
+        <is>
+          <t>la Dirección General de Programas Turísticos y Alianzas Estratégicas de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O726" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0725-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0726-2026</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+      <c r="J727" t="inlineStr"/>
+      <c r="K727" t="inlineStr"/>
+      <c r="L727" t="inlineStr"/>
+      <c r="M727" t="inlineStr">
+        <is>
+          <t>Seguro Facultativo</t>
+        </is>
+      </c>
+      <c r="N727" t="inlineStr">
+        <is>
+          <t>el Colegio de Estudios Científicos y Tecnológicos del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O727" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0726-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -36466,7 +36466,7 @@
       <c r="I687" t="inlineStr"/>
       <c r="J687" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K687" t="inlineStr"/>
@@ -37075,7 +37075,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="L696" t="inlineStr"/>
+      <c r="L696" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="M696" t="inlineStr">
         <is>
           <t>Muebles de Oficina y Estantería</t>
@@ -37140,7 +37144,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="L697" t="inlineStr"/>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="M697" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -37205,7 +37213,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="L698" t="inlineStr"/>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="M698" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores Otros Bienes Muebles</t>
@@ -37270,7 +37282,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="L699" t="inlineStr"/>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="M699" t="inlineStr">
         <is>
           <t>Refacciones y Accesorios Menores de Edificios</t>
@@ -37330,7 +37346,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr"/>
       <c r="M700" t="inlineStr">
         <is>
@@ -37391,7 +37411,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr"/>
       <c r="M701" t="inlineStr">
         <is>
@@ -37452,7 +37476,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr"/>
       <c r="M702" t="inlineStr">
         <is>
@@ -37513,7 +37541,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr"/>
       <c r="M703" t="inlineStr">
         <is>
@@ -37574,7 +37606,11 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr"/>
       <c r="M704" t="inlineStr">
         <is>
@@ -37919,7 +37955,11 @@
       </c>
       <c r="H710" t="inlineStr"/>
       <c r="I710" t="inlineStr"/>
-      <c r="J710" t="inlineStr"/>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K710" t="inlineStr"/>
       <c r="L710" t="inlineStr"/>
       <c r="M710" t="inlineStr">
@@ -37976,7 +38016,11 @@
       </c>
       <c r="H711" t="inlineStr"/>
       <c r="I711" t="inlineStr"/>
-      <c r="J711" t="inlineStr"/>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K711" t="inlineStr"/>
       <c r="L711" t="inlineStr"/>
       <c r="M711" t="inlineStr">
@@ -38033,7 +38077,11 @@
       </c>
       <c r="H712" t="inlineStr"/>
       <c r="I712" t="inlineStr"/>
-      <c r="J712" t="inlineStr"/>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K712" t="inlineStr"/>
       <c r="L712" t="inlineStr"/>
       <c r="M712" t="inlineStr">
@@ -38090,7 +38138,11 @@
       </c>
       <c r="H713" t="inlineStr"/>
       <c r="I713" t="inlineStr"/>
-      <c r="J713" t="inlineStr"/>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr"/>
       <c r="M713" t="inlineStr">
@@ -38147,7 +38199,11 @@
       </c>
       <c r="H714" t="inlineStr"/>
       <c r="I714" t="inlineStr"/>
-      <c r="J714" t="inlineStr"/>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K714" t="inlineStr"/>
       <c r="L714" t="inlineStr"/>
       <c r="M714" t="inlineStr">
@@ -38204,7 +38260,11 @@
       </c>
       <c r="H715" t="inlineStr"/>
       <c r="I715" t="inlineStr"/>
-      <c r="J715" t="inlineStr"/>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K715" t="inlineStr"/>
       <c r="L715" t="inlineStr"/>
       <c r="M715" t="inlineStr">
@@ -38261,7 +38321,11 @@
       </c>
       <c r="H716" t="inlineStr"/>
       <c r="I716" t="inlineStr"/>
-      <c r="J716" t="inlineStr"/>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K716" t="inlineStr"/>
       <c r="L716" t="inlineStr"/>
       <c r="M716" t="inlineStr">
@@ -38318,7 +38382,11 @@
       </c>
       <c r="H717" t="inlineStr"/>
       <c r="I717" t="inlineStr"/>
-      <c r="J717" t="inlineStr"/>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
       <c r="K717" t="inlineStr"/>
       <c r="L717" t="inlineStr"/>
       <c r="M717" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O727"/>
+  <dimension ref="A1:O732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38975,6 +38975,291 @@
         </is>
       </c>
     </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0727-2026</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+      <c r="J728" t="inlineStr"/>
+      <c r="K728" t="inlineStr"/>
+      <c r="L728" t="inlineStr"/>
+      <c r="M728" t="inlineStr">
+        <is>
+          <t>Mobiliario para el Bachillerato del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="N728" t="inlineStr">
+        <is>
+          <t>el Instituto Hidalguense de la Infraestructura Física Educativa</t>
+        </is>
+      </c>
+      <c r="O728" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0727-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0728-2026</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+      <c r="J729" t="inlineStr"/>
+      <c r="K729" t="inlineStr"/>
+      <c r="L729" t="inlineStr"/>
+      <c r="M729" t="inlineStr">
+        <is>
+          <t>Activos Intangibles, Servicios de Informática, Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N729" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal de Mejora Regulatoria en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O729" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0728-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0729-2026</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+      <c r="J730" t="inlineStr"/>
+      <c r="K730" t="inlineStr"/>
+      <c r="L730" t="inlineStr"/>
+      <c r="M730" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N730" t="inlineStr">
+        <is>
+          <t>la Dirección General de Control y Seguimiento a Entidades Paraestatales en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O730" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0729-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0730-2026</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+      <c r="J731" t="inlineStr"/>
+      <c r="K731" t="inlineStr"/>
+      <c r="L731" t="inlineStr"/>
+      <c r="M731" t="inlineStr">
+        <is>
+          <t>Servicios de Informática</t>
+        </is>
+      </c>
+      <c r="N731" t="inlineStr">
+        <is>
+          <t>la Dirección General de Control y Seguimiento a Entidades Paraestatales de la Unidad de Planeación y Prospectiva en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O731" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0730-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0731-2026</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+      <c r="J732" t="inlineStr"/>
+      <c r="K732" t="inlineStr"/>
+      <c r="L732" t="inlineStr"/>
+      <c r="M732" t="inlineStr">
+        <is>
+          <t>Fortalecimiento Tecnológico para el Desarrollo de Proyectos de Infraestructura</t>
+        </is>
+      </c>
+      <c r="N732" t="inlineStr">
+        <is>
+          <t>la Dirección de Infraestructura y Fomento Turístico dependiente de la Subsecretaría de Turismo de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O732" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0731-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -37351,7 +37351,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L700" t="inlineStr"/>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="M700" t="inlineStr">
         <is>
           <t>Materiales, Accesorios y Suministros de Laboratorio</t>
@@ -37416,7 +37420,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr"/>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="M701" t="inlineStr">
         <is>
           <t>Vehículos y Equipo Terrestre</t>
@@ -37481,7 +37489,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr"/>
+      <c r="L702" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="M702" t="inlineStr">
         <is>
           <t>Formas Valoradas</t>
@@ -37546,7 +37558,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L703" t="inlineStr"/>
+      <c r="L703" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="M703" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -37611,7 +37627,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="L704" t="inlineStr"/>
+      <c r="L704" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="M704" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -37655,7 +37675,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr"/>
       <c r="M705" t="inlineStr">
         <is>
@@ -37716,7 +37740,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr"/>
       <c r="M706" t="inlineStr">
         <is>
@@ -37777,7 +37805,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr"/>
       <c r="M707" t="inlineStr">
         <is>
@@ -37838,7 +37870,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr"/>
       <c r="M708" t="inlineStr">
         <is>
@@ -37899,7 +37935,11 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr"/>
       <c r="M709" t="inlineStr">
         <is>
@@ -38443,7 +38483,11 @@
       </c>
       <c r="H718" t="inlineStr"/>
       <c r="I718" t="inlineStr"/>
-      <c r="J718" t="inlineStr"/>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K718" t="inlineStr"/>
       <c r="L718" t="inlineStr"/>
       <c r="M718" t="inlineStr">
@@ -38500,7 +38544,11 @@
       </c>
       <c r="H719" t="inlineStr"/>
       <c r="I719" t="inlineStr"/>
-      <c r="J719" t="inlineStr"/>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K719" t="inlineStr"/>
       <c r="L719" t="inlineStr"/>
       <c r="M719" t="inlineStr">
@@ -38557,7 +38605,11 @@
       </c>
       <c r="H720" t="inlineStr"/>
       <c r="I720" t="inlineStr"/>
-      <c r="J720" t="inlineStr"/>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K720" t="inlineStr"/>
       <c r="L720" t="inlineStr"/>
       <c r="M720" t="inlineStr">
@@ -38614,7 +38666,11 @@
       </c>
       <c r="H721" t="inlineStr"/>
       <c r="I721" t="inlineStr"/>
-      <c r="J721" t="inlineStr"/>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K721" t="inlineStr"/>
       <c r="L721" t="inlineStr"/>
       <c r="M721" t="inlineStr">
@@ -38671,7 +38727,11 @@
       </c>
       <c r="H722" t="inlineStr"/>
       <c r="I722" t="inlineStr"/>
-      <c r="J722" t="inlineStr"/>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K722" t="inlineStr"/>
       <c r="L722" t="inlineStr"/>
       <c r="M722" t="inlineStr">
@@ -38728,7 +38788,11 @@
       </c>
       <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr"/>
-      <c r="J723" t="inlineStr"/>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K723" t="inlineStr"/>
       <c r="L723" t="inlineStr"/>
       <c r="M723" t="inlineStr">
@@ -38785,7 +38849,11 @@
       </c>
       <c r="H724" t="inlineStr"/>
       <c r="I724" t="inlineStr"/>
-      <c r="J724" t="inlineStr"/>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K724" t="inlineStr"/>
       <c r="L724" t="inlineStr"/>
       <c r="M724" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O732"/>
+  <dimension ref="A1:O735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38910,7 +38910,11 @@
       </c>
       <c r="H725" t="inlineStr"/>
       <c r="I725" t="inlineStr"/>
-      <c r="J725" t="inlineStr"/>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K725" t="inlineStr"/>
       <c r="L725" t="inlineStr"/>
       <c r="M725" t="inlineStr">
@@ -38967,7 +38971,11 @@
       </c>
       <c r="H726" t="inlineStr"/>
       <c r="I726" t="inlineStr"/>
-      <c r="J726" t="inlineStr"/>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K726" t="inlineStr"/>
       <c r="L726" t="inlineStr"/>
       <c r="M726" t="inlineStr">
@@ -39024,7 +39032,11 @@
       </c>
       <c r="H727" t="inlineStr"/>
       <c r="I727" t="inlineStr"/>
-      <c r="J727" t="inlineStr"/>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
       <c r="K727" t="inlineStr"/>
       <c r="L727" t="inlineStr"/>
       <c r="M727" t="inlineStr">
@@ -39328,6 +39340,177 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0732-2026</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+      <c r="J733" t="inlineStr"/>
+      <c r="K733" t="inlineStr"/>
+      <c r="L733" t="inlineStr"/>
+      <c r="M733" t="inlineStr">
+        <is>
+          <t>Servicio de Geolocalización</t>
+        </is>
+      </c>
+      <c r="N733" t="inlineStr">
+        <is>
+          <t>la Central Estatal de Información, Investigación e Inteligencia de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O733" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0732-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0733-2026</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr"/>
+      <c r="J734" t="inlineStr"/>
+      <c r="K734" t="inlineStr"/>
+      <c r="L734" t="inlineStr"/>
+      <c r="M734" t="inlineStr">
+        <is>
+          <t>Formas Valoradas</t>
+        </is>
+      </c>
+      <c r="N734" t="inlineStr">
+        <is>
+          <t>el Sistema de Transporte Convencional de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O734" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0733-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0734-2026</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+      <c r="J735" t="inlineStr"/>
+      <c r="K735" t="inlineStr"/>
+      <c r="L735" t="inlineStr"/>
+      <c r="M735" t="inlineStr">
+        <is>
+          <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N735" t="inlineStr">
+        <is>
+          <t>el Sistema Integrado de Transporte Masivo de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O735" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0734-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -36469,7 +36469,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr"/>
       <c r="M687" t="inlineStr">
         <is>
@@ -37680,7 +37684,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="L705" t="inlineStr"/>
+      <c r="L705" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="M705" t="inlineStr">
         <is>
           <t>Activos Intangibles (Sistema Integral de Enseñanza, Aprendizaje y Certificación del Idioma Inglés)</t>
@@ -37875,7 +37883,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="L708" t="inlineStr"/>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="M708" t="inlineStr">
         <is>
           <t>Otros Equipos, Equipo Educacional y Recreativo</t>
@@ -37940,7 +37952,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="L709" t="inlineStr"/>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="M709" t="inlineStr">
         <is>
           <t>Maquinaria y Equipo de Seguridad Pública (Segundo Procedimiento)</t>
@@ -38000,7 +38016,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr"/>
       <c r="M710" t="inlineStr">
         <is>
@@ -38058,7 +38078,7 @@
       <c r="I711" t="inlineStr"/>
       <c r="J711" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="K711" t="inlineStr"/>
@@ -38122,7 +38142,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr"/>
       <c r="M712" t="inlineStr">
         <is>
@@ -38183,7 +38207,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr"/>
       <c r="M713" t="inlineStr">
         <is>
@@ -38244,7 +38272,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr"/>
       <c r="M714" t="inlineStr">
         <is>
@@ -38305,7 +38337,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr"/>
       <c r="M715" t="inlineStr">
         <is>
@@ -38366,7 +38402,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr"/>
       <c r="M716" t="inlineStr">
         <is>
@@ -38427,7 +38467,11 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr"/>
       <c r="M717" t="inlineStr">
         <is>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -39137,7 +39137,11 @@
       </c>
       <c r="H728" t="inlineStr"/>
       <c r="I728" t="inlineStr"/>
-      <c r="J728" t="inlineStr"/>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="K728" t="inlineStr"/>
       <c r="L728" t="inlineStr"/>
       <c r="M728" t="inlineStr">
@@ -39194,7 +39198,11 @@
       </c>
       <c r="H729" t="inlineStr"/>
       <c r="I729" t="inlineStr"/>
-      <c r="J729" t="inlineStr"/>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="K729" t="inlineStr"/>
       <c r="L729" t="inlineStr"/>
       <c r="M729" t="inlineStr">
@@ -39251,7 +39259,11 @@
       </c>
       <c r="H730" t="inlineStr"/>
       <c r="I730" t="inlineStr"/>
-      <c r="J730" t="inlineStr"/>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="K730" t="inlineStr"/>
       <c r="L730" t="inlineStr"/>
       <c r="M730" t="inlineStr">
@@ -39308,7 +39320,11 @@
       </c>
       <c r="H731" t="inlineStr"/>
       <c r="I731" t="inlineStr"/>
-      <c r="J731" t="inlineStr"/>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="K731" t="inlineStr"/>
       <c r="L731" t="inlineStr"/>
       <c r="M731" t="inlineStr">
@@ -39365,7 +39381,11 @@
       </c>
       <c r="H732" t="inlineStr"/>
       <c r="I732" t="inlineStr"/>
-      <c r="J732" t="inlineStr"/>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
       <c r="K732" t="inlineStr"/>
       <c r="L732" t="inlineStr"/>
       <c r="M732" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O735"/>
+  <dimension ref="A1:O743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39575,6 +39575,462 @@
         </is>
       </c>
     </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0735-2026</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+      <c r="J736" t="inlineStr"/>
+      <c r="K736" t="inlineStr"/>
+      <c r="L736" t="inlineStr"/>
+      <c r="M736" t="inlineStr">
+        <is>
+          <t>Estudios e Investigaciones</t>
+        </is>
+      </c>
+      <c r="N736" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Planeación y Evaluación de la Secretaría de Educación Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O736" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0735-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0736-2026</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+      <c r="J737" t="inlineStr"/>
+      <c r="K737" t="inlineStr"/>
+      <c r="L737" t="inlineStr"/>
+      <c r="M737" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería, Otros Equipos, Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N737" t="inlineStr">
+        <is>
+          <t>el Consejo de Ciencia, Tecnología e Innovación de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O737" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0736-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0737-2026</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+      <c r="J738" t="inlineStr"/>
+      <c r="K738" t="inlineStr"/>
+      <c r="L738" t="inlineStr"/>
+      <c r="M738" t="inlineStr">
+        <is>
+          <t>Material Eléctrico, Otros Materiales y Artículos de Construcción y Reparación</t>
+        </is>
+      </c>
+      <c r="N738" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O738" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0737-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0738-2026</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+      <c r="J739" t="inlineStr"/>
+      <c r="K739" t="inlineStr"/>
+      <c r="L739" t="inlineStr"/>
+      <c r="M739" t="inlineStr">
+        <is>
+          <t>Material de Limpieza (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N739" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O739" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0738-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0739-2026</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+      <c r="J740" t="inlineStr"/>
+      <c r="K740" t="inlineStr"/>
+      <c r="L740" t="inlineStr"/>
+      <c r="M740" t="inlineStr">
+        <is>
+          <t>Equipo para el Taller de Topografía</t>
+        </is>
+      </c>
+      <c r="N740" t="inlineStr">
+        <is>
+          <t>el Instituto Tecnológico Superior del Oriente del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O740" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0739-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0740-2026</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+      <c r="J741" t="inlineStr"/>
+      <c r="K741" t="inlineStr"/>
+      <c r="L741" t="inlineStr"/>
+      <c r="M741" t="inlineStr">
+        <is>
+          <t>Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N741" t="inlineStr">
+        <is>
+          <t>la Coordinación General de Normatividad y Entidades Paraestatales en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O741" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0740-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0741-2026</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+      <c r="J742" t="inlineStr"/>
+      <c r="K742" t="inlineStr"/>
+      <c r="L742" t="inlineStr"/>
+      <c r="M742" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N742" t="inlineStr">
+        <is>
+          <t>la Coordinación General de Normatividad y Entidades Paraestatales en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O742" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0741-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0742-2026</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+      <c r="J743" t="inlineStr"/>
+      <c r="K743" t="inlineStr"/>
+      <c r="L743" t="inlineStr"/>
+      <c r="M743" t="inlineStr">
+        <is>
+          <t>Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N743" t="inlineStr">
+        <is>
+          <t>la Dirección General de Control y Seguimiento a Entidades Paraestatales en conjunto con la Dirección General de Administración de la Unidad de Planeación y Prospectiva del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O743" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0742-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -38021,7 +38021,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="L710" t="inlineStr"/>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="M710" t="inlineStr">
         <is>
           <t>Blancos y Otros Productos Textiles, Excepto Prendas de Vestir (colchones)</t>
@@ -38532,7 +38536,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr"/>
       <c r="M718" t="inlineStr">
         <is>
@@ -38593,7 +38601,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr"/>
       <c r="M719" t="inlineStr">
         <is>
@@ -38654,7 +38666,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr"/>
       <c r="M720" t="inlineStr">
         <is>
@@ -38712,7 +38728,7 @@
       <c r="I721" t="inlineStr"/>
       <c r="J721" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K721" t="inlineStr"/>
@@ -38776,7 +38792,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr"/>
       <c r="M722" t="inlineStr">
         <is>
@@ -38837,7 +38857,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr"/>
       <c r="M723" t="inlineStr">
         <is>
@@ -38898,7 +38922,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr"/>
       <c r="M724" t="inlineStr">
         <is>
@@ -38959,7 +38987,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr"/>
       <c r="M725" t="inlineStr">
         <is>
@@ -39020,7 +39052,11 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr"/>
       <c r="M726" t="inlineStr">
         <is>
@@ -39078,7 +39114,7 @@
       <c r="I727" t="inlineStr"/>
       <c r="J727" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="K727" t="inlineStr"/>
@@ -39442,7 +39478,11 @@
       </c>
       <c r="H733" t="inlineStr"/>
       <c r="I733" t="inlineStr"/>
-      <c r="J733" t="inlineStr"/>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="K733" t="inlineStr"/>
       <c r="L733" t="inlineStr"/>
       <c r="M733" t="inlineStr">
@@ -39499,7 +39539,11 @@
       </c>
       <c r="H734" t="inlineStr"/>
       <c r="I734" t="inlineStr"/>
-      <c r="J734" t="inlineStr"/>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="K734" t="inlineStr"/>
       <c r="L734" t="inlineStr"/>
       <c r="M734" t="inlineStr">
@@ -39556,7 +39600,11 @@
       </c>
       <c r="H735" t="inlineStr"/>
       <c r="I735" t="inlineStr"/>
-      <c r="J735" t="inlineStr"/>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="K735" t="inlineStr"/>
       <c r="L735" t="inlineStr"/>
       <c r="M735" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O743"/>
+  <dimension ref="A1:O753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39057,7 +39057,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L726" t="inlineStr"/>
+      <c r="L726" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
       <c r="M726" t="inlineStr">
         <is>
           <t>Servicios Integrales</t>
@@ -40079,6 +40083,576 @@
         </is>
       </c>
     </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0743-2026</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+      <c r="J744" t="inlineStr"/>
+      <c r="K744" t="inlineStr"/>
+      <c r="L744" t="inlineStr"/>
+      <c r="M744" t="inlineStr">
+        <is>
+          <t>Reparación Mayor de Vehículos</t>
+        </is>
+      </c>
+      <c r="N744" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O744" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0743-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0744-2026</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+      <c r="J745" t="inlineStr"/>
+      <c r="K745" t="inlineStr"/>
+      <c r="L745" t="inlineStr"/>
+      <c r="M745" t="inlineStr">
+        <is>
+          <t>Asignaciones Presupuestarias al Poder Ejecutivo (Sombreros y Chalecos)</t>
+        </is>
+      </c>
+      <c r="N745" t="inlineStr">
+        <is>
+          <t>la Secretaría de Contraloría del Poder Ejecutivo del Gobierno del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O745" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0744-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0745-2026</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+      <c r="J746" t="inlineStr"/>
+      <c r="K746" t="inlineStr"/>
+      <c r="L746" t="inlineStr"/>
+      <c r="M746" t="inlineStr">
+        <is>
+          <t>Vestuario y Uniformes</t>
+        </is>
+      </c>
+      <c r="N746" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O746" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0745-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0746-2026</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+      <c r="J747" t="inlineStr"/>
+      <c r="K747" t="inlineStr"/>
+      <c r="L747" t="inlineStr"/>
+      <c r="M747" t="inlineStr">
+        <is>
+          <t>Refacciones y Accesorios Menores Otros Bienes Muebles (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N747" t="inlineStr">
+        <is>
+          <t>la Comisión de Agua y Alcantarillado de Sistemas Intermunicipales</t>
+        </is>
+      </c>
+      <c r="O747" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0746-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0747-2026</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+      <c r="J748" t="inlineStr"/>
+      <c r="K748" t="inlineStr"/>
+      <c r="L748" t="inlineStr"/>
+      <c r="M748" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N748" t="inlineStr">
+        <is>
+          <t>el Secretariado Ejecutivo del Consejo Estatal de Seguridad Pública de la Secretaría de Gobierno del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O748" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0747-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0748-2026</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+      <c r="J749" t="inlineStr"/>
+      <c r="K749" t="inlineStr"/>
+      <c r="L749" t="inlineStr"/>
+      <c r="M749" t="inlineStr">
+        <is>
+          <t>Herramientas y Máquinas-Herramienta (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N749" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O749" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0748-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0749-2026</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+      <c r="J750" t="inlineStr"/>
+      <c r="K750" t="inlineStr"/>
+      <c r="L750" t="inlineStr"/>
+      <c r="M750" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N750" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O750" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0749-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0750-2026</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+      <c r="J751" t="inlineStr"/>
+      <c r="K751" t="inlineStr"/>
+      <c r="L751" t="inlineStr"/>
+      <c r="M751" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N751" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O751" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0750-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0751-2026</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+      <c r="J752" t="inlineStr"/>
+      <c r="K752" t="inlineStr"/>
+      <c r="L752" t="inlineStr"/>
+      <c r="M752" t="inlineStr">
+        <is>
+          <t>Equipo Médico y de Laboratorio (Segundo Procedimiento)</t>
+        </is>
+      </c>
+      <c r="N752" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica de Tula-Tepeji</t>
+        </is>
+      </c>
+      <c r="O752" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0751-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0752-2026</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+      <c r="J753" t="inlineStr"/>
+      <c r="K753" t="inlineStr"/>
+      <c r="L753" t="inlineStr"/>
+      <c r="M753" t="inlineStr">
+        <is>
+          <t>Material Eléctrico</t>
+        </is>
+      </c>
+      <c r="N753" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Pachuca</t>
+        </is>
+      </c>
+      <c r="O753" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0752-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -38281,7 +38281,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="L714" t="inlineStr"/>
+      <c r="L714" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M714" t="inlineStr">
         <is>
           <t>Bienes Informáticos, Licencias Informáticas e Intelectuales</t>
@@ -38411,7 +38415,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="L716" t="inlineStr"/>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M716" t="inlineStr">
         <is>
           <t>Maquinaria y Equipo Industrial</t>
@@ -38476,7 +38484,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="L717" t="inlineStr"/>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M717" t="inlineStr">
         <is>
           <t>Equipos y Aparatos de Audio</t>
@@ -38541,7 +38553,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L718" t="inlineStr"/>
+      <c r="L718" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M718" t="inlineStr">
         <is>
           <t>Materiales y Útiles Consumibles para el Procesamiento en Equipos y Bienes Informáticos</t>
@@ -38606,7 +38622,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L719" t="inlineStr"/>
+      <c r="L719" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M719" t="inlineStr">
         <is>
           <t>Silla y Mesa Escolar</t>
@@ -38671,7 +38691,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L720" t="inlineStr"/>
+      <c r="L720" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M720" t="inlineStr">
         <is>
           <t>Mobiliario y Equipo de Aulas Didácticas</t>
@@ -38797,7 +38821,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L722" t="inlineStr"/>
+      <c r="L722" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M722" t="inlineStr">
         <is>
           <t>Material de Oficina (Segundo Procedimiento)</t>
@@ -38862,7 +38890,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L723" t="inlineStr"/>
+      <c r="L723" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="M723" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O753"/>
+  <dimension ref="A1:O763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40685,6 +40685,576 @@
         </is>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0753-2026</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+      <c r="J754" t="inlineStr"/>
+      <c r="K754" t="inlineStr"/>
+      <c r="L754" t="inlineStr"/>
+      <c r="M754" t="inlineStr">
+        <is>
+          <t>Servicios Integrales</t>
+        </is>
+      </c>
+      <c r="N754" t="inlineStr">
+        <is>
+          <t>la Dirección General de Programas Turísticos y Alianzas Estratégicas de la Secretaría de Turismo del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O754" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0753-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0754-2026</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+      <c r="J755" t="inlineStr"/>
+      <c r="K755" t="inlineStr"/>
+      <c r="L755" t="inlineStr"/>
+      <c r="M755" t="inlineStr">
+        <is>
+          <t>Maquinaria y Equipo de Seguridad Pública, Equipos y Aparatos de Comunicación y Telecomunicación, Herramientas y Maquinas – Herramientas</t>
+        </is>
+      </c>
+      <c r="N755" t="inlineStr">
+        <is>
+          <t>la Agencia de Investigación Criminal de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O755" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0754-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0755-2026</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+      <c r="J756" t="inlineStr"/>
+      <c r="K756" t="inlineStr"/>
+      <c r="L756" t="inlineStr"/>
+      <c r="M756" t="inlineStr">
+        <is>
+          <t>Maquinaria y Equipo de Seguridad Pública</t>
+        </is>
+      </c>
+      <c r="N756" t="inlineStr">
+        <is>
+          <t>la Unidad Especializada en el Combate al Secuestro de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O756" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0755-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0756-2026</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+      <c r="J757" t="inlineStr"/>
+      <c r="K757" t="inlineStr"/>
+      <c r="L757" t="inlineStr"/>
+      <c r="M757" t="inlineStr">
+        <is>
+          <t>Capacitación, Servicios de Contabilidad, Auditoría y Servicios Relacionados</t>
+        </is>
+      </c>
+      <c r="N757" t="inlineStr">
+        <is>
+          <t>de la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O757" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0756-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0757-2026</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+      <c r="J758" t="inlineStr"/>
+      <c r="K758" t="inlineStr"/>
+      <c r="L758" t="inlineStr"/>
+      <c r="M758" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N758" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O758" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0757-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0758-2026</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+      <c r="J759" t="inlineStr"/>
+      <c r="K759" t="inlineStr"/>
+      <c r="L759" t="inlineStr"/>
+      <c r="M759" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N759" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O759" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0758-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0759-2026</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+      <c r="J760" t="inlineStr"/>
+      <c r="K760" t="inlineStr"/>
+      <c r="L760" t="inlineStr"/>
+      <c r="M760" t="inlineStr">
+        <is>
+          <t>Servicios de Informática</t>
+        </is>
+      </c>
+      <c r="N760" t="inlineStr">
+        <is>
+          <t>la Junta General de Asistencia del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O760" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0759-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0760-2026</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+      <c r="J761" t="inlineStr"/>
+      <c r="K761" t="inlineStr"/>
+      <c r="L761" t="inlineStr"/>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>Sustancias Químicas</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>el Hospital del Niño DIF Hidalgo del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O761" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0760-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0761-2026</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+      <c r="J762" t="inlineStr"/>
+      <c r="K762" t="inlineStr"/>
+      <c r="L762" t="inlineStr"/>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>la Dirección de Alimentación y Desarrollo Comunitario del Sistema para el Desarrollo Integral de la Familia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O762" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0761-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0762-2026</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+      <c r="J763" t="inlineStr"/>
+      <c r="K763" t="inlineStr"/>
+      <c r="L763" t="inlineStr"/>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>la Dirección General de Recursos Materiales de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O763" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0762-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -36474,7 +36474,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="L687" t="inlineStr"/>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="M687" t="inlineStr">
         <is>
           <t>Bienes Informáticos</t>
@@ -38085,7 +38089,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr"/>
       <c r="M711" t="inlineStr">
         <is>
@@ -38693,7 +38701,7 @@
       </c>
       <c r="L720" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="M720" t="inlineStr">
@@ -38959,7 +38967,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L724" t="inlineStr"/>
+      <c r="L724" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="M724" t="inlineStr">
         <is>
           <t>Mantenimiento de Maquinaria y Equipo</t>
@@ -39024,7 +39036,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="L725" t="inlineStr"/>
+      <c r="L725" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="M725" t="inlineStr">
         <is>
           <t>Otros Materiales y Artículos de Construcción y Reparación</t>
@@ -39153,7 +39169,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr"/>
       <c r="M727" t="inlineStr">
         <is>
@@ -39214,7 +39234,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr"/>
       <c r="M728" t="inlineStr">
         <is>
@@ -39275,7 +39299,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr"/>
       <c r="M729" t="inlineStr">
         <is>
@@ -39336,7 +39364,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr"/>
       <c r="M730" t="inlineStr">
         <is>
@@ -39397,7 +39429,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr"/>
       <c r="M731" t="inlineStr">
         <is>
@@ -39458,7 +39494,11 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr"/>
       <c r="M732" t="inlineStr">
         <is>
@@ -39697,7 +39737,11 @@
       </c>
       <c r="H736" t="inlineStr"/>
       <c r="I736" t="inlineStr"/>
-      <c r="J736" t="inlineStr"/>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K736" t="inlineStr"/>
       <c r="L736" t="inlineStr"/>
       <c r="M736" t="inlineStr">
@@ -39754,7 +39798,11 @@
       </c>
       <c r="H737" t="inlineStr"/>
       <c r="I737" t="inlineStr"/>
-      <c r="J737" t="inlineStr"/>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K737" t="inlineStr"/>
       <c r="L737" t="inlineStr"/>
       <c r="M737" t="inlineStr">
@@ -39811,7 +39859,11 @@
       </c>
       <c r="H738" t="inlineStr"/>
       <c r="I738" t="inlineStr"/>
-      <c r="J738" t="inlineStr"/>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K738" t="inlineStr"/>
       <c r="L738" t="inlineStr"/>
       <c r="M738" t="inlineStr">
@@ -39868,7 +39920,11 @@
       </c>
       <c r="H739" t="inlineStr"/>
       <c r="I739" t="inlineStr"/>
-      <c r="J739" t="inlineStr"/>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K739" t="inlineStr"/>
       <c r="L739" t="inlineStr"/>
       <c r="M739" t="inlineStr">
@@ -39925,7 +39981,11 @@
       </c>
       <c r="H740" t="inlineStr"/>
       <c r="I740" t="inlineStr"/>
-      <c r="J740" t="inlineStr"/>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K740" t="inlineStr"/>
       <c r="L740" t="inlineStr"/>
       <c r="M740" t="inlineStr">
@@ -39982,7 +40042,11 @@
       </c>
       <c r="H741" t="inlineStr"/>
       <c r="I741" t="inlineStr"/>
-      <c r="J741" t="inlineStr"/>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K741" t="inlineStr"/>
       <c r="L741" t="inlineStr"/>
       <c r="M741" t="inlineStr">

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O763"/>
+  <dimension ref="A1:O773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39174,7 +39174,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="L727" t="inlineStr"/>
+      <c r="L727" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="M727" t="inlineStr">
         <is>
           <t>Seguro Facultativo</t>
@@ -40103,7 +40107,11 @@
       </c>
       <c r="H742" t="inlineStr"/>
       <c r="I742" t="inlineStr"/>
-      <c r="J742" t="inlineStr"/>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K742" t="inlineStr"/>
       <c r="L742" t="inlineStr"/>
       <c r="M742" t="inlineStr">
@@ -40160,7 +40168,11 @@
       </c>
       <c r="H743" t="inlineStr"/>
       <c r="I743" t="inlineStr"/>
-      <c r="J743" t="inlineStr"/>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
       <c r="K743" t="inlineStr"/>
       <c r="L743" t="inlineStr"/>
       <c r="M743" t="inlineStr">
@@ -41319,6 +41331,576 @@
         </is>
       </c>
     </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0763-2026</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+      <c r="J764" t="inlineStr"/>
+      <c r="K764" t="inlineStr"/>
+      <c r="L764" t="inlineStr"/>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>la Universidad Digital del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O764" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0763-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0764-2026</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+      <c r="J765" t="inlineStr"/>
+      <c r="K765" t="inlineStr"/>
+      <c r="L765" t="inlineStr"/>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>Material de Oficina</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>el Centro de Justicia para las Mujeres del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O765" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0764-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0765-2026</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+      <c r="J766" t="inlineStr"/>
+      <c r="K766" t="inlineStr"/>
+      <c r="L766" t="inlineStr"/>
+      <c r="M766" t="inlineStr">
+        <is>
+          <t>Equipo de Construcción</t>
+        </is>
+      </c>
+      <c r="N766" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Maquinaria para el Desarrollo</t>
+        </is>
+      </c>
+      <c r="O766" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0765-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0766-2026</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+      <c r="J767" t="inlineStr"/>
+      <c r="K767" t="inlineStr"/>
+      <c r="L767" t="inlineStr"/>
+      <c r="M767" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N767" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Maquinaria para el Desarrollo</t>
+        </is>
+      </c>
+      <c r="O767" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0766-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0767-2026</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+      <c r="J768" t="inlineStr"/>
+      <c r="K768" t="inlineStr"/>
+      <c r="L768" t="inlineStr"/>
+      <c r="M768" t="inlineStr">
+        <is>
+          <t>Equipo de Construcción</t>
+        </is>
+      </c>
+      <c r="N768" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Maquinaria para el Desarrollo</t>
+        </is>
+      </c>
+      <c r="O768" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0767-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0768-2026</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+      <c r="J769" t="inlineStr"/>
+      <c r="K769" t="inlineStr"/>
+      <c r="L769" t="inlineStr"/>
+      <c r="M769" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina y Estantería</t>
+        </is>
+      </c>
+      <c r="N769" t="inlineStr">
+        <is>
+          <t>la Comisión Estatal de Vivienda</t>
+        </is>
+      </c>
+      <c r="O769" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0768-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0769-2026</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+      <c r="J770" t="inlineStr"/>
+      <c r="K770" t="inlineStr"/>
+      <c r="L770" t="inlineStr"/>
+      <c r="M770" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N770" t="inlineStr">
+        <is>
+          <t>el Centro Estatal de Evaluación y Control de Confianza de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O770" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0769-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0770-2026</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+      <c r="J771" t="inlineStr"/>
+      <c r="K771" t="inlineStr"/>
+      <c r="L771" t="inlineStr"/>
+      <c r="M771" t="inlineStr">
+        <is>
+          <t>Licencias Informáticas e Intelectuales</t>
+        </is>
+      </c>
+      <c r="N771" t="inlineStr">
+        <is>
+          <t>la Policía Industrial Bancaria del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O771" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0770-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0771-2026</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+      <c r="J772" t="inlineStr"/>
+      <c r="K772" t="inlineStr"/>
+      <c r="L772" t="inlineStr"/>
+      <c r="M772" t="inlineStr">
+        <is>
+          <t>Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N772" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Tulancingo</t>
+        </is>
+      </c>
+      <c r="O772" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0771-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0772-2026</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+      <c r="J773" t="inlineStr"/>
+      <c r="K773" t="inlineStr"/>
+      <c r="L773" t="inlineStr"/>
+      <c r="M773" t="inlineStr">
+        <is>
+          <t>Equipamiento para el Fortalecimiento a la Infraestructura Educativa</t>
+        </is>
+      </c>
+      <c r="N773" t="inlineStr">
+        <is>
+          <t>la Universidad Politécnica de Francisco I. Madero</t>
+        </is>
+      </c>
+      <c r="O773" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0772-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O773"/>
+  <dimension ref="A1:O781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38094,7 +38094,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="L711" t="inlineStr"/>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="M711" t="inlineStr">
         <is>
           <t>Estudios e Investigaciones</t>
@@ -38763,7 +38767,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr"/>
       <c r="M721" t="inlineStr">
         <is>
@@ -39308,7 +39316,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="L729" t="inlineStr"/>
+      <c r="L729" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="M729" t="inlineStr">
         <is>
           <t>Activos Intangibles, Servicios de Informática, Servicios Integrales</t>
@@ -39373,7 +39385,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="L730" t="inlineStr"/>
+      <c r="L730" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="M730" t="inlineStr">
         <is>
           <t>Licencias Informáticas e Intelectuales</t>
@@ -39438,7 +39454,11 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="L731" t="inlineStr"/>
+      <c r="L731" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="M731" t="inlineStr">
         <is>
           <t>Servicios de Informática</t>
@@ -39563,7 +39583,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr"/>
       <c r="M733" t="inlineStr">
         <is>
@@ -39624,7 +39648,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr"/>
       <c r="M734" t="inlineStr">
         <is>
@@ -39685,7 +39713,11 @@
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr"/>
       <c r="M735" t="inlineStr">
         <is>
@@ -40229,7 +40261,11 @@
       </c>
       <c r="H744" t="inlineStr"/>
       <c r="I744" t="inlineStr"/>
-      <c r="J744" t="inlineStr"/>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K744" t="inlineStr"/>
       <c r="L744" t="inlineStr"/>
       <c r="M744" t="inlineStr">
@@ -40286,7 +40322,11 @@
       </c>
       <c r="H745" t="inlineStr"/>
       <c r="I745" t="inlineStr"/>
-      <c r="J745" t="inlineStr"/>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K745" t="inlineStr"/>
       <c r="L745" t="inlineStr"/>
       <c r="M745" t="inlineStr">
@@ -40343,7 +40383,11 @@
       </c>
       <c r="H746" t="inlineStr"/>
       <c r="I746" t="inlineStr"/>
-      <c r="J746" t="inlineStr"/>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K746" t="inlineStr"/>
       <c r="L746" t="inlineStr"/>
       <c r="M746" t="inlineStr">
@@ -40400,7 +40444,11 @@
       </c>
       <c r="H747" t="inlineStr"/>
       <c r="I747" t="inlineStr"/>
-      <c r="J747" t="inlineStr"/>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K747" t="inlineStr"/>
       <c r="L747" t="inlineStr"/>
       <c r="M747" t="inlineStr">
@@ -40457,7 +40505,11 @@
       </c>
       <c r="H748" t="inlineStr"/>
       <c r="I748" t="inlineStr"/>
-      <c r="J748" t="inlineStr"/>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K748" t="inlineStr"/>
       <c r="L748" t="inlineStr"/>
       <c r="M748" t="inlineStr">
@@ -40514,7 +40566,11 @@
       </c>
       <c r="H749" t="inlineStr"/>
       <c r="I749" t="inlineStr"/>
-      <c r="J749" t="inlineStr"/>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K749" t="inlineStr"/>
       <c r="L749" t="inlineStr"/>
       <c r="M749" t="inlineStr">
@@ -40571,7 +40627,11 @@
       </c>
       <c r="H750" t="inlineStr"/>
       <c r="I750" t="inlineStr"/>
-      <c r="J750" t="inlineStr"/>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K750" t="inlineStr"/>
       <c r="L750" t="inlineStr"/>
       <c r="M750" t="inlineStr">
@@ -40628,7 +40688,11 @@
       </c>
       <c r="H751" t="inlineStr"/>
       <c r="I751" t="inlineStr"/>
-      <c r="J751" t="inlineStr"/>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K751" t="inlineStr"/>
       <c r="L751" t="inlineStr"/>
       <c r="M751" t="inlineStr">
@@ -40685,7 +40749,11 @@
       </c>
       <c r="H752" t="inlineStr"/>
       <c r="I752" t="inlineStr"/>
-      <c r="J752" t="inlineStr"/>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K752" t="inlineStr"/>
       <c r="L752" t="inlineStr"/>
       <c r="M752" t="inlineStr">
@@ -40742,7 +40810,11 @@
       </c>
       <c r="H753" t="inlineStr"/>
       <c r="I753" t="inlineStr"/>
-      <c r="J753" t="inlineStr"/>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
       <c r="K753" t="inlineStr"/>
       <c r="L753" t="inlineStr"/>
       <c r="M753" t="inlineStr">
@@ -41901,6 +41973,462 @@
         </is>
       </c>
     </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0773-2026</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+      <c r="J774" t="inlineStr"/>
+      <c r="K774" t="inlineStr"/>
+      <c r="L774" t="inlineStr"/>
+      <c r="M774" t="inlineStr">
+        <is>
+          <t>Servicio Global</t>
+        </is>
+      </c>
+      <c r="N774" t="inlineStr">
+        <is>
+          <t>la Dirección General de Administración de la Oficialía Mayor del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O774" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0773-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0774-2026</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+      <c r="J775" t="inlineStr"/>
+      <c r="K775" t="inlineStr"/>
+      <c r="L775" t="inlineStr"/>
+      <c r="M775" t="inlineStr">
+        <is>
+          <t>Bienes Informáticos</t>
+        </is>
+      </c>
+      <c r="N775" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O775" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0774-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0775-2026</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr"/>
+      <c r="J776" t="inlineStr"/>
+      <c r="K776" t="inlineStr"/>
+      <c r="L776" t="inlineStr"/>
+      <c r="M776" t="inlineStr">
+        <is>
+          <t>Activos Intangibles</t>
+        </is>
+      </c>
+      <c r="N776" t="inlineStr">
+        <is>
+          <t>la Coordinación General del Distrito de Educación, Salud, Ciencia, Tecnología e Innovación</t>
+        </is>
+      </c>
+      <c r="O776" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0775-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0776-2026</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+      <c r="J777" t="inlineStr"/>
+      <c r="K777" t="inlineStr"/>
+      <c r="L777" t="inlineStr"/>
+      <c r="M777" t="inlineStr">
+        <is>
+          <t>Medicinas y Productos Farmacéuticos</t>
+        </is>
+      </c>
+      <c r="N777" t="inlineStr">
+        <is>
+          <t>el Instituto de Formación Profesional de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O777" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0776-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0777-2026</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="inlineStr"/>
+      <c r="J778" t="inlineStr"/>
+      <c r="K778" t="inlineStr"/>
+      <c r="L778" t="inlineStr"/>
+      <c r="M778" t="inlineStr">
+        <is>
+          <t>Vehículos y Equipo Terrestre</t>
+        </is>
+      </c>
+      <c r="N778" t="inlineStr">
+        <is>
+          <t>la Subsecretaría de Operación Policial de la Secretaría de Seguridad Pública del Poder Ejecutivo del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O778" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0777-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0778-2026</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+      <c r="J779" t="inlineStr"/>
+      <c r="K779" t="inlineStr"/>
+      <c r="L779" t="inlineStr"/>
+      <c r="M779" t="inlineStr">
+        <is>
+          <t>Muebles de Oficina, Estantería y Equipo de Administración</t>
+        </is>
+      </c>
+      <c r="N779" t="inlineStr">
+        <is>
+          <t>el Colegio de Educación Profesional Técnica del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O779" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0778-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0779-2026</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+      <c r="J780" t="inlineStr"/>
+      <c r="K780" t="inlineStr"/>
+      <c r="L780" t="inlineStr"/>
+      <c r="M780" t="inlineStr">
+        <is>
+          <t>Equipos y Aparatos Audiovisuales</t>
+        </is>
+      </c>
+      <c r="N780" t="inlineStr">
+        <is>
+          <t>la Universidad Tecnológica Minera de Zimapán</t>
+        </is>
+      </c>
+      <c r="O780" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0779-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>EA-913003989-N0780-2026</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="inlineStr"/>
+      <c r="J781" t="inlineStr"/>
+      <c r="K781" t="inlineStr"/>
+      <c r="L781" t="inlineStr"/>
+      <c r="M781" t="inlineStr">
+        <is>
+          <t>Servicios de Informática</t>
+        </is>
+      </c>
+      <c r="N781" t="inlineStr">
+        <is>
+          <t>la Procuraduría General de Justicia del Estado de Hidalgo</t>
+        </is>
+      </c>
+      <c r="O781" t="inlineStr">
+        <is>
+          <t>pdfs/EA-913003989-N0780-2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/licitaciones.xlsx
+++ b/data/licitaciones.xlsx
@@ -40871,7 +40871,11 @@
       </c>
       <c r="H754" t="inlineStr"/>
       <c r="I754" t="inlineStr"/>
-      <c r="J754" t="inlineStr"/>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K754" t="inlineStr"/>
       <c r="L754" t="inlineStr"/>
       <c r="M754" t="inlineStr">
@@ -40928,7 +40932,11 @@
       </c>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr"/>
-      <c r="J755" t="inlineStr"/>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K755" t="inlineStr"/>
       <c r="L755" t="inlineStr"/>
       <c r="M755" t="inlineStr">
@@ -40985,7 +40993,11 @@
       </c>
       <c r="H756" t="inlineStr"/>
       <c r="I756" t="inlineStr"/>
-      <c r="J756" t="inlineStr"/>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K756" t="inlineStr"/>
       <c r="L756" t="inlineStr"/>
       <c r="M756" t="inlineStr">
@@ -41042,7 +41054,11 @@
       </c>
       <c r="H757" t="inlineStr"/>
       <c r="I757" t="inlineStr"/>
-      <c r="J757" t="inlineStr"/>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K757" t="inlineStr"/>
       <c r="L757" t="inlineStr"/>
       <c r="M757" t="inlineStr">
@@ -41099,7 +41115,11 @@
       </c>
       <c r="H758" t="inlineStr"/>
       <c r="I758" t="inlineStr"/>
-      <c r="J758" t="inlineStr"/>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K758" t="inlineStr"/>
       <c r="L758" t="inlineStr"/>
       <c r="M758" t="inlineStr">
@@ -41156,7 +41176,11 @@
       </c>
       <c r="H759" t="inlineStr"/>
       <c r="I759" t="inlineStr"/>
-      <c r="J759" t="inlineStr"/>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K759" t="inlineStr"/>
       <c r="L759" t="inlineStr"/>
       <c r="M759" t="inlineStr">
@@ -41213,7 +41237,11 @@
       </c>
       <c r="H760" t="inlineStr"/>
       <c r="I760" t="inlineStr"/>
-      <c r="J760" t="inlineStr"/>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K760" t="inlineStr"/>
       <c r="L760" t="inlineStr"/>
       <c r="M760" t="inlineStr">
@@ -41270,7 +41298,11 @@
       </c>
       <c r="H761" t="inlineStr"/>
       <c r="I761" t="inlineStr"/>
-      <c r="J761" t="inlineStr"/>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K761" t="inlineStr"/>
       <c r="L761" t="inlineStr"/>
       <c r="M761" t="inlineStr">
@@ -41327,7 +41359,11 @@
       </c>
       <c r="H762" t="inlineStr"/>
       <c r="I762" t="inlineStr"/>
-      <c r="J762" t="inlineStr"/>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K762" t="inlineStr"/>
       <c r="L762" t="inlineStr"/>
       <c r="M762" t="inlineStr">
@@ -41384,7 +41420,11 @@
       </c>
       <c r="H763" t="inlineStr"/>
       <c r="I763" t="inlineStr"/>
-      <c r="J763" t="inlineStr"/>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="K763" t="inlineStr"/>
       <c r="L763" t="inlineStr"/>
       <c r="M763" t="inlineStr">
